--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,16 +434,33 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="B3" t="str">
+        <v>巴西</v>
+      </c>
+      <c r="C3" t="str">
+        <v>TikTok</v>
+      </c>
+      <c r="D3" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,9 +485,423 @@
         <v>sort</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>巴西_美客多__item__1775655178925_b6dbuk</v>
+      </c>
+      <c r="B2" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C2" t="str">
+        <v>汇损</v>
+      </c>
+      <c r="D2" t="str">
+        <v>number</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>巴西_美客多__item__1775655178925_d4gauu</v>
+      </c>
+      <c r="B3" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C3" t="str">
+        <v>活动费率</v>
+      </c>
+      <c r="D3" t="str">
+        <v>number</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>巴西_美客多__item__1775655178925_lj3exs</v>
+      </c>
+      <c r="B4" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C4" t="str">
+        <v>折扣</v>
+      </c>
+      <c r="D4" t="str">
+        <v>number</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>巴西_美客多__item__1775655178925_qfbetw</v>
+      </c>
+      <c r="B5" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C5" t="str">
+        <v>提现费率</v>
+      </c>
+      <c r="D5" t="str">
+        <v>number</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>巴西_美客多__item__1775655178925_ta67tt</v>
+      </c>
+      <c r="B6" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C6" t="str">
+        <v>交易费率</v>
+      </c>
+      <c r="D6" t="str">
+        <v>number</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>巴西_美客多__item__1775655178925_18be97</v>
+      </c>
+      <c r="B7" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C7" t="str">
+        <v>汇率</v>
+      </c>
+      <c r="D7" t="str">
+        <v>number</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
+      </c>
+      <c r="B8" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C8" t="str">
+        <v>税率</v>
+      </c>
+      <c r="D8" t="str">
+        <v>number</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
+      </c>
+      <c r="B9" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C9" t="str">
+        <v>贴单费用</v>
+      </c>
+      <c r="D9" t="str">
+        <v>number</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>巴西_美客多__item__1775655178925_4tnm24</v>
+      </c>
+      <c r="B10" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C10" t="str">
+        <v>是否包邮</v>
+      </c>
+      <c r="D10" t="str">
+        <v>boolean</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>是</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
+      </c>
+      <c r="B11" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C11" t="str">
+        <v>汇损</v>
+      </c>
+      <c r="D11" t="str">
+        <v>number</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
+      </c>
+      <c r="B12" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C12" t="str">
+        <v>活动费率</v>
+      </c>
+      <c r="D12" t="str">
+        <v>number</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
+      </c>
+      <c r="B13" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C13" t="str">
+        <v>折扣</v>
+      </c>
+      <c r="D13" t="str">
+        <v>number</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
+      </c>
+      <c r="B14" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C14" t="str">
+        <v>提现费率</v>
+      </c>
+      <c r="D14" t="str">
+        <v>number</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>巴西_TikTok__item__1775655438790_two67j</v>
+      </c>
+      <c r="B15" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C15" t="str">
+        <v>交易费率</v>
+      </c>
+      <c r="D15" t="str">
+        <v>number</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
+      </c>
+      <c r="B16" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C16" t="str">
+        <v>汇率</v>
+      </c>
+      <c r="D16" t="str">
+        <v>number</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>巴西_TikTok__item__1775655438790_swod7s</v>
+      </c>
+      <c r="B17" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C17" t="str">
+        <v>税率</v>
+      </c>
+      <c r="D17" t="str">
+        <v>number</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
+      </c>
+      <c r="B18" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C18" t="str">
+        <v>贴单费用</v>
+      </c>
+      <c r="D18" t="str">
+        <v>number</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>巴西_TikTok__item__1775655438790_dpk097</v>
+      </c>
+      <c r="B19" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C19" t="str">
+        <v>是否包邮</v>
+      </c>
+      <c r="D19" t="str">
+        <v>boolean</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>是</v>
+      </c>
+      <c r="G19">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -499,7 +499,7 @@
         <v>number</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F2" t="str">
         <v>2</v>
@@ -522,7 +522,7 @@
         <v>number</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F3" t="str">
         <v>2</v>
@@ -545,7 +545,7 @@
         <v>number</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F4" t="str">
         <v>2</v>
@@ -568,7 +568,7 @@
         <v>number</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F5" t="str">
         <v>2</v>
@@ -591,7 +591,7 @@
         <v>number</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F6" t="str">
         <v>2</v>
@@ -614,7 +614,7 @@
         <v>number</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F7" t="str">
         <v>2</v>
@@ -637,7 +637,7 @@
         <v>number</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F8" t="str">
         <v>2</v>
@@ -660,7 +660,7 @@
         <v>number</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>R$</v>
       </c>
       <c r="F9" t="str">
         <v>2</v>

--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -5,6 +5,11 @@
   <sheets>
     <sheet name="preset_groups" sheetId="1" r:id="rId1"/>
     <sheet name="preset_items" sheetId="2" r:id="rId2"/>
+    <sheet name="template_tables" sheetId="3" r:id="rId3"/>
+    <sheet name="tpl_ml_br_fixed_fee" sheetId="4" r:id="rId4"/>
+    <sheet name="tpl_ml_br_shipping_fee" sheetId="5" r:id="rId5"/>
+    <sheet name="tpl_ml_br_ship_fast_79" sheetId="6" r:id="rId6"/>
+    <sheet name="tpl_ml_br_commission" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -33,7 +38,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -460,7 +469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:J22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -482,6 +491,15 @@
         <v>value</v>
       </c>
       <c r="G1" t="str">
+        <v>rule_mode</v>
+      </c>
+      <c r="H1" t="str">
+        <v>rule_table_id</v>
+      </c>
+      <c r="I1" t="str">
+        <v>rule_config</v>
+      </c>
+      <c r="J1" t="str">
         <v>sort</v>
       </c>
     </row>
@@ -504,42 +522,60 @@
       <c r="F2" t="str">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>巴西_美客多__item__1775655178925_d4gauu</v>
+        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
       </c>
       <c r="B3" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C3" t="str">
-        <v>活动费率</v>
+        <v>汇损</v>
       </c>
       <c r="D3" t="str">
         <v>number</v>
       </c>
       <c r="E3" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>巴西_美客多__item__1775655178925_lj3exs</v>
+        <v>巴西_美客多__item__1775655178925_d4gauu</v>
       </c>
       <c r="B4" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C4" t="str">
-        <v>折扣</v>
+        <v>活动费率</v>
       </c>
       <c r="D4" t="str">
         <v>number</v>
@@ -550,42 +586,60 @@
       <c r="F4" t="str">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>3</v>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>巴西_美客多__item__1775655178925_qfbetw</v>
+        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
       </c>
       <c r="B5" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C5" t="str">
-        <v>提现费率</v>
+        <v>活动费率</v>
       </c>
       <c r="D5" t="str">
         <v>number</v>
       </c>
       <c r="E5" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5">
         <v>2</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>巴西_美客多__item__1775655178925_ta67tt</v>
+        <v>巴西_美客多__item__1775655178925_lj3exs</v>
       </c>
       <c r="B6" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C6" t="str">
-        <v>交易费率</v>
+        <v>折扣</v>
       </c>
       <c r="D6" t="str">
         <v>number</v>
@@ -596,42 +650,60 @@
       <c r="F6" t="str">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>5</v>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>巴西_美客多__item__1775655178925_18be97</v>
+        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
       </c>
       <c r="B7" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C7" t="str">
-        <v>汇率</v>
+        <v>折扣</v>
       </c>
       <c r="D7" t="str">
         <v>number</v>
       </c>
       <c r="E7" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
+        <v>巴西_美客多__item__1775655178925_qfbetw</v>
       </c>
       <c r="B8" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C8" t="str">
-        <v>税率</v>
+        <v>提现费率</v>
       </c>
       <c r="D8" t="str">
         <v>number</v>
@@ -642,65 +714,92 @@
       <c r="F8" t="str">
         <v>2</v>
       </c>
-      <c r="G8">
-        <v>7</v>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
+        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
       </c>
       <c r="B9" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C9" t="str">
-        <v>贴单费用</v>
+        <v>提现费率</v>
       </c>
       <c r="D9" t="str">
         <v>number</v>
       </c>
       <c r="E9" t="str">
-        <v>R$</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>8</v>
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>巴西_美客多__item__1775655178925_4tnm24</v>
+        <v>巴西_美客多__item__1775655178925_ta67tt</v>
       </c>
       <c r="B10" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C10" t="str">
-        <v>是否包邮</v>
+        <v>交易费率</v>
       </c>
       <c r="D10" t="str">
-        <v>boolean</v>
+        <v>number</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F10" t="str">
-        <v>是</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
+        <v>巴西_TikTok__item__1775655438790_two67j</v>
       </c>
       <c r="B11" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C11" t="str">
-        <v>汇损</v>
+        <v>交易费率</v>
       </c>
       <c r="D11" t="str">
         <v>number</v>
@@ -711,42 +810,60 @@
       <c r="F11" t="str">
         <v/>
       </c>
-      <c r="G11">
-        <v>1</v>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
+        <v>巴西_美客多__item__1775655178925_18be97</v>
       </c>
       <c r="B12" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C12" t="str">
-        <v>活动费率</v>
+        <v>汇率</v>
       </c>
       <c r="D12" t="str">
         <v>number</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12">
         <v>2</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
+        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
       </c>
       <c r="B13" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C13" t="str">
-        <v>折扣</v>
+        <v>汇率</v>
       </c>
       <c r="D13" t="str">
         <v>number</v>
@@ -757,42 +874,60 @@
       <c r="F13" t="str">
         <v/>
       </c>
-      <c r="G13">
-        <v>3</v>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13">
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
+        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
       </c>
       <c r="B14" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C14" t="str">
-        <v>提现费率</v>
+        <v>税率</v>
       </c>
       <c r="D14" t="str">
         <v>number</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>巴西_TikTok__item__1775655438790_two67j</v>
+        <v>巴西_TikTok__item__1775655438790_swod7s</v>
       </c>
       <c r="B15" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C15" t="str">
-        <v>交易费率</v>
+        <v>税率</v>
       </c>
       <c r="D15" t="str">
         <v>number</v>
@@ -803,42 +938,60 @@
       <c r="F15" t="str">
         <v/>
       </c>
-      <c r="G15">
-        <v>5</v>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
+        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
       </c>
       <c r="B16" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C16" t="str">
-        <v>汇率</v>
+        <v>贴单费用</v>
       </c>
       <c r="D16" t="str">
         <v>number</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>R$</v>
       </c>
       <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>巴西_TikTok__item__1775655438790_swod7s</v>
+        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
       </c>
       <c r="B17" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C17" t="str">
-        <v>税率</v>
+        <v>贴单费用</v>
       </c>
       <c r="D17" t="str">
         <v>number</v>
@@ -849,31 +1002,49 @@
       <c r="F17" t="str">
         <v/>
       </c>
-      <c r="G17">
-        <v>7</v>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
+        <v>巴西_美客多__item__1775655178925_4tnm24</v>
       </c>
       <c r="B18" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C18" t="str">
-        <v>贴单费用</v>
+        <v>是否包邮</v>
       </c>
       <c r="D18" t="str">
-        <v>number</v>
+        <v>boolean</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18">
-        <v>8</v>
+        <v>是</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18">
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -895,13 +1066,1758 @@
       <c r="F19" t="str">
         <v>是</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19">
         <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>巴西_美客多__item__seller_shipping</v>
+      </c>
+      <c r="B20" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C20" t="str">
+        <v>卖家支付运费</v>
+      </c>
+      <c r="D20" t="str">
+        <v>rule</v>
+      </c>
+      <c r="E20" t="str">
+        <v>R$</v>
+      </c>
+      <c r="F20" t="str">
+        <v>if({是否包邮} == "是", 0, 查表("巴西美客多运费补贴表", {折后售价}, {重量}))</v>
+      </c>
+      <c r="G20" t="str">
+        <v>condition</v>
+      </c>
+      <c r="H20" t="str">
+        <v>ml_br_shipping_fee</v>
+      </c>
+      <c r="I20" t="str">
+        <v>{"field":"是否包邮","operator":"eq","compareValue":"是","thenAction":{"kind":"fixed","value":"0","tableId":"","args":[]},"elseAction":{"kind":"table","value":"","tableId":"ml_br_shipping_fee","args":["折后售价","重量"]}}</v>
+      </c>
+      <c r="J20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>巴西_美客多__item__commission_rate</v>
+      </c>
+      <c r="B21" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C21" t="str">
+        <v>佣金费率</v>
+      </c>
+      <c r="D21" t="str">
+        <v>rule</v>
+      </c>
+      <c r="E21" t="str">
+        <v>%</v>
+      </c>
+      <c r="F21" t="str">
+        <v>查表("巴西美客多佣金表", {类目}, {广告类型})</v>
+      </c>
+      <c r="G21" t="str">
+        <v>advanced</v>
+      </c>
+      <c r="H21" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="I21" t="str">
+        <v>{"expression":"查表(\"巴西美客多佣金表\", {类目}, {广告类型})"}</v>
+      </c>
+      <c r="J21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>巴西_美客多__item__fixed_surcharge</v>
+      </c>
+      <c r="B22" t="str">
+        <v>巴西_美客多</v>
+      </c>
+      <c r="C22" t="str">
+        <v>固定附加费</v>
+      </c>
+      <c r="D22" t="str">
+        <v>rule</v>
+      </c>
+      <c r="E22" t="str">
+        <v>R$</v>
+      </c>
+      <c r="F22" t="str">
+        <v>if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表("巴西美客多固定附加费表", {折后售价}))</v>
+      </c>
+      <c r="G22" t="str">
+        <v>advanced</v>
+      </c>
+      <c r="H22" t="str">
+        <v>ml_br_fixed_fee</v>
+      </c>
+      <c r="I22" t="str">
+        <v>{"expression":"if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表(\"巴西美客多固定附加费表\", {折后售价}))"}</v>
+      </c>
+      <c r="J22">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>sheet_name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rule_type</v>
+      </c>
+      <c r="E1" t="str">
+        <v>country</v>
+      </c>
+      <c r="F1" t="str">
+        <v>platform</v>
+      </c>
+      <c r="G1" t="str">
+        <v>value_unit</v>
+      </c>
+      <c r="H1" t="str">
+        <v>x_axis_label</v>
+      </c>
+      <c r="I1" t="str">
+        <v>y_axis_label</v>
+      </c>
+      <c r="J1" t="str">
+        <v>source_url</v>
+      </c>
+      <c r="K1" t="str">
+        <v>enabled</v>
+      </c>
+      <c r="L1" t="str">
+        <v>sort</v>
+      </c>
+      <c r="M1" t="str">
+        <v>remark</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ml_br_fixed_fee</v>
+      </c>
+      <c r="B2" t="str">
+        <v>巴西美客多固定附加费表</v>
+      </c>
+      <c r="C2" t="str">
+        <v>tpl_ml_br_fixed_fee</v>
+      </c>
+      <c r="D2" t="str">
+        <v>range_1d</v>
+      </c>
+      <c r="E2" t="str">
+        <v>巴西</v>
+      </c>
+      <c r="F2" t="str">
+        <v>美客多</v>
+      </c>
+      <c r="G2" t="str">
+        <v>R$</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v>https://www.mercadolivre.com.br/ajuda/870</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="str">
+        <v>来源页当前说明：79 以上不收固定费，12.50 以下按售价一半收取固定费。</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ml_br_shipping_fee</v>
+      </c>
+      <c r="B3" t="str">
+        <v>巴西美客多运费补贴表</v>
+      </c>
+      <c r="C3" t="str">
+        <v>tpl_ml_br_shipping_fee</v>
+      </c>
+      <c r="D3" t="str">
+        <v>range_2d</v>
+      </c>
+      <c r="E3" t="str">
+        <v>巴西</v>
+      </c>
+      <c r="F3" t="str">
+        <v>美客多</v>
+      </c>
+      <c r="G3" t="str">
+        <v>R$</v>
+      </c>
+      <c r="H3" t="str">
+        <v>售价</v>
+      </c>
+      <c r="I3" t="str">
+        <v>重量</v>
+      </c>
+      <c r="J3" t="str">
+        <v>https://www.mercadolivre.com.br/ajuda/40538</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="str">
+        <v>按重量和售价区间命中一行运费值。</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ml_br_shipping_fast_under_79</v>
+      </c>
+      <c r="B4" t="str">
+        <v>巴西美客多 79 以下快速免邮表</v>
+      </c>
+      <c r="C4" t="str">
+        <v>tpl_ml_br_ship_fast_79</v>
+      </c>
+      <c r="D4" t="str">
+        <v>range_1d</v>
+      </c>
+      <c r="E4" t="str">
+        <v>巴西</v>
+      </c>
+      <c r="F4" t="str">
+        <v>美客多</v>
+      </c>
+      <c r="G4" t="str">
+        <v>R$</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>https://www.mercadolivre.com.br/ajuda/40538</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4" t="str">
+        <v>官方 79 以下可选快速免邮成本，按重量区间查值。</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B5" t="str">
+        <v>巴西美客多佣金表</v>
+      </c>
+      <c r="C5" t="str">
+        <v>tpl_ml_br_commission</v>
+      </c>
+      <c r="D5" t="str">
+        <v>enum_range</v>
+      </c>
+      <c r="E5" t="str">
+        <v>巴西</v>
+      </c>
+      <c r="F5" t="str">
+        <v>美客多</v>
+      </c>
+      <c r="G5" t="str">
+        <v>%</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>https://www.mercadolivre.com.br/ajuda/tarifas-e-faturamento_1044</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5" t="str">
+        <v>来源页当前只明确给出费率范围：Clássico 为 10%~14%，Premium 为 15%~19%。类目细表未直接给出，这里先不写死猜测值。</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>x_min</v>
+      </c>
+      <c r="B1" t="str">
+        <v>x_max</v>
+      </c>
+      <c r="C1" t="str">
+        <v>value</v>
+      </c>
+      <c r="D1" t="str">
+        <v>remark</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="B2" t="str">
+        <v>29</v>
+      </c>
+      <c r="C2" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="D2" t="str">
+        <v>来源页还说明商品售价至少应为 R$ 8。</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>29</v>
+      </c>
+      <c r="B3" t="str">
+        <v>50</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6.50</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>50</v>
+      </c>
+      <c r="B4" t="str">
+        <v>79</v>
+      </c>
+      <c r="C4" t="str">
+        <v>6.75</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I30"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>重量\售价</v>
+      </c>
+      <c r="B1" t="str">
+        <v>19</v>
+      </c>
+      <c r="C1" t="str">
+        <v>49</v>
+      </c>
+      <c r="D1" t="str">
+        <v>79</v>
+      </c>
+      <c r="E1" t="str">
+        <v>100</v>
+      </c>
+      <c r="F1" t="str">
+        <v>120</v>
+      </c>
+      <c r="G1" t="str">
+        <v>150</v>
+      </c>
+      <c r="H1" t="str">
+        <v>200</v>
+      </c>
+      <c r="I1" t="str">
+        <v>最后区间及以上</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="B2" t="str">
+        <v>5.65</v>
+      </c>
+      <c r="C2" t="str">
+        <v>6.55</v>
+      </c>
+      <c r="D2" t="str">
+        <v>7.75</v>
+      </c>
+      <c r="E2" t="str">
+        <v>12.35</v>
+      </c>
+      <c r="F2" t="str">
+        <v>14.35</v>
+      </c>
+      <c r="G2" t="str">
+        <v>16.45</v>
+      </c>
+      <c r="H2" t="str">
+        <v>18.45</v>
+      </c>
+      <c r="I2" t="str">
+        <v>20.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="str">
+        <v>5.95</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6.65</v>
+      </c>
+      <c r="D3" t="str">
+        <v>7.85</v>
+      </c>
+      <c r="E3" t="str">
+        <v>13.25</v>
+      </c>
+      <c r="F3" t="str">
+        <v>15.45</v>
+      </c>
+      <c r="G3" t="str">
+        <v>17.65</v>
+      </c>
+      <c r="H3" t="str">
+        <v>19.85</v>
+      </c>
+      <c r="I3" t="str">
+        <v>22.55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>6.05</v>
+      </c>
+      <c r="C4" t="str">
+        <v>6.75</v>
+      </c>
+      <c r="D4" t="str">
+        <v>7.95</v>
+      </c>
+      <c r="E4" t="str">
+        <v>13.85</v>
+      </c>
+      <c r="F4" t="str">
+        <v>16.15</v>
+      </c>
+      <c r="G4" t="str">
+        <v>18.45</v>
+      </c>
+      <c r="H4" t="str">
+        <v>20.75</v>
+      </c>
+      <c r="I4" t="str">
+        <v>23.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>6.15</v>
+      </c>
+      <c r="C5" t="str">
+        <v>6.85</v>
+      </c>
+      <c r="D5" t="str">
+        <v>8.05</v>
+      </c>
+      <c r="E5" t="str">
+        <v>14.15</v>
+      </c>
+      <c r="F5" t="str">
+        <v>16.45</v>
+      </c>
+      <c r="G5" t="str">
+        <v>18.85</v>
+      </c>
+      <c r="H5" t="str">
+        <v>21.15</v>
+      </c>
+      <c r="I5" t="str">
+        <v>24.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>6.95</v>
+      </c>
+      <c r="D6" t="str">
+        <v>8.15</v>
+      </c>
+      <c r="E6" t="str">
+        <v>14.45</v>
+      </c>
+      <c r="F6" t="str">
+        <v>16.85</v>
+      </c>
+      <c r="G6" t="str">
+        <v>19.25</v>
+      </c>
+      <c r="H6" t="str">
+        <v>21.65</v>
+      </c>
+      <c r="I6" t="str">
+        <v>24.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>3</v>
+      </c>
+      <c r="B7" t="str">
+        <v>6.35</v>
+      </c>
+      <c r="C7" t="str">
+        <v>7.95</v>
+      </c>
+      <c r="D7" t="str">
+        <v>8.55</v>
+      </c>
+      <c r="E7" t="str">
+        <v>15.75</v>
+      </c>
+      <c r="F7" t="str">
+        <v>18.35</v>
+      </c>
+      <c r="G7" t="str">
+        <v>21.05</v>
+      </c>
+      <c r="H7" t="str">
+        <v>23.65</v>
+      </c>
+      <c r="I7" t="str">
+        <v>26.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>4</v>
+      </c>
+      <c r="B8" t="str">
+        <v>6.45</v>
+      </c>
+      <c r="C8" t="str">
+        <v>8.15</v>
+      </c>
+      <c r="D8" t="str">
+        <v>8.95</v>
+      </c>
+      <c r="E8" t="str">
+        <v>17.05</v>
+      </c>
+      <c r="F8" t="str">
+        <v>19.85</v>
+      </c>
+      <c r="G8" t="str">
+        <v>22.65</v>
+      </c>
+      <c r="H8" t="str">
+        <v>25.55</v>
+      </c>
+      <c r="I8" t="str">
+        <v>28.35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>6.55</v>
+      </c>
+      <c r="C9" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="D9" t="str">
+        <v>9.75</v>
+      </c>
+      <c r="E9" t="str">
+        <v>18.45</v>
+      </c>
+      <c r="F9" t="str">
+        <v>21.55</v>
+      </c>
+      <c r="G9" t="str">
+        <v>24.65</v>
+      </c>
+      <c r="H9" t="str">
+        <v>27.75</v>
+      </c>
+      <c r="I9" t="str">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6</v>
+      </c>
+      <c r="B10" t="str">
+        <v>6.65</v>
+      </c>
+      <c r="C10" t="str">
+        <v>8.55</v>
+      </c>
+      <c r="D10" t="str">
+        <v>9.95</v>
+      </c>
+      <c r="E10" t="str">
+        <v>25.45</v>
+      </c>
+      <c r="F10" t="str">
+        <v>28.55</v>
+      </c>
+      <c r="G10" t="str">
+        <v>32.65</v>
+      </c>
+      <c r="H10" t="str">
+        <v>35.75</v>
+      </c>
+      <c r="I10" t="str">
+        <v>39.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>7</v>
+      </c>
+      <c r="B11" t="str">
+        <v>6.75</v>
+      </c>
+      <c r="C11" t="str">
+        <v>8.75</v>
+      </c>
+      <c r="D11" t="str">
+        <v>10.15</v>
+      </c>
+      <c r="E11" t="str">
+        <v>27.05</v>
+      </c>
+      <c r="F11" t="str">
+        <v>31.05</v>
+      </c>
+      <c r="G11" t="str">
+        <v>36.05</v>
+      </c>
+      <c r="H11" t="str">
+        <v>40.05</v>
+      </c>
+      <c r="I11" t="str">
+        <v>44.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>8</v>
+      </c>
+      <c r="B12" t="str">
+        <v>6.85</v>
+      </c>
+      <c r="C12" t="str">
+        <v>8.95</v>
+      </c>
+      <c r="D12" t="str">
+        <v>10.35</v>
+      </c>
+      <c r="E12" t="str">
+        <v>28.85</v>
+      </c>
+      <c r="F12" t="str">
+        <v>33.65</v>
+      </c>
+      <c r="G12" t="str">
+        <v>38.45</v>
+      </c>
+      <c r="H12" t="str">
+        <v>43.25</v>
+      </c>
+      <c r="I12" t="str">
+        <v>48.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>9</v>
+      </c>
+      <c r="B13" t="str">
+        <v>6.95</v>
+      </c>
+      <c r="C13" t="str">
+        <v>9.15</v>
+      </c>
+      <c r="D13" t="str">
+        <v>10.55</v>
+      </c>
+      <c r="E13" t="str">
+        <v>29.65</v>
+      </c>
+      <c r="F13" t="str">
+        <v>34.55</v>
+      </c>
+      <c r="G13" t="str">
+        <v>39.55</v>
+      </c>
+      <c r="H13" t="str">
+        <v>44.45</v>
+      </c>
+      <c r="I13" t="str">
+        <v>49.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>7.05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>9.55</v>
+      </c>
+      <c r="D14" t="str">
+        <v>10.95</v>
+      </c>
+      <c r="E14" t="str">
+        <v>41.25</v>
+      </c>
+      <c r="F14" t="str">
+        <v>48.05</v>
+      </c>
+      <c r="G14" t="str">
+        <v>54.95</v>
+      </c>
+      <c r="H14" t="str">
+        <v>61.75</v>
+      </c>
+      <c r="I14" t="str">
+        <v>68.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>13</v>
+      </c>
+      <c r="B15" t="str">
+        <v>7.15</v>
+      </c>
+      <c r="C15" t="str">
+        <v>9.95</v>
+      </c>
+      <c r="D15" t="str">
+        <v>11.35</v>
+      </c>
+      <c r="E15" t="str">
+        <v>42.15</v>
+      </c>
+      <c r="F15" t="str">
+        <v>49.25</v>
+      </c>
+      <c r="G15" t="str">
+        <v>56.25</v>
+      </c>
+      <c r="H15" t="str">
+        <v>63.25</v>
+      </c>
+      <c r="I15" t="str">
+        <v>70.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>7.25</v>
+      </c>
+      <c r="C16" t="str">
+        <v>10.15</v>
+      </c>
+      <c r="D16" t="str">
+        <v>11.55</v>
+      </c>
+      <c r="E16" t="str">
+        <v>45.05</v>
+      </c>
+      <c r="F16" t="str">
+        <v>52.45</v>
+      </c>
+      <c r="G16" t="str">
+        <v>59.95</v>
+      </c>
+      <c r="H16" t="str">
+        <v>67.45</v>
+      </c>
+      <c r="I16" t="str">
+        <v>74.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>17</v>
+      </c>
+      <c r="B17" t="str">
+        <v>7.35</v>
+      </c>
+      <c r="C17" t="str">
+        <v>10.35</v>
+      </c>
+      <c r="D17" t="str">
+        <v>11.75</v>
+      </c>
+      <c r="E17" t="str">
+        <v>48.55</v>
+      </c>
+      <c r="F17" t="str">
+        <v>56.05</v>
+      </c>
+      <c r="G17" t="str">
+        <v>63.55</v>
+      </c>
+      <c r="H17" t="str">
+        <v>70.75</v>
+      </c>
+      <c r="I17" t="str">
+        <v>78.65</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>20</v>
+      </c>
+      <c r="B18" t="str">
+        <v>7.45</v>
+      </c>
+      <c r="C18" t="str">
+        <v>10.55</v>
+      </c>
+      <c r="D18" t="str">
+        <v>11.95</v>
+      </c>
+      <c r="E18" t="str">
+        <v>54.75</v>
+      </c>
+      <c r="F18" t="str">
+        <v>63.85</v>
+      </c>
+      <c r="G18" t="str">
+        <v>72.95</v>
+      </c>
+      <c r="H18" t="str">
+        <v>82.05</v>
+      </c>
+      <c r="I18" t="str">
+        <v>91.15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>25</v>
+      </c>
+      <c r="B19" t="str">
+        <v>7.65</v>
+      </c>
+      <c r="C19" t="str">
+        <v>10.95</v>
+      </c>
+      <c r="D19" t="str">
+        <v>12.15</v>
+      </c>
+      <c r="E19" t="str">
+        <v>64.05</v>
+      </c>
+      <c r="F19" t="str">
+        <v>75.05</v>
+      </c>
+      <c r="G19" t="str">
+        <v>84.75</v>
+      </c>
+      <c r="H19" t="str">
+        <v>95.35</v>
+      </c>
+      <c r="I19" t="str">
+        <v>105.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>30</v>
+      </c>
+      <c r="B20" t="str">
+        <v>7.75</v>
+      </c>
+      <c r="C20" t="str">
+        <v>11.15</v>
+      </c>
+      <c r="D20" t="str">
+        <v>12.35</v>
+      </c>
+      <c r="E20" t="str">
+        <v>65.95</v>
+      </c>
+      <c r="F20" t="str">
+        <v>75.45</v>
+      </c>
+      <c r="G20" t="str">
+        <v>85.55</v>
+      </c>
+      <c r="H20" t="str">
+        <v>96.25</v>
+      </c>
+      <c r="I20" t="str">
+        <v>106.95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>40</v>
+      </c>
+      <c r="B21" t="str">
+        <v>7.85</v>
+      </c>
+      <c r="C21" t="str">
+        <v>11.35</v>
+      </c>
+      <c r="D21" t="str">
+        <v>12.55</v>
+      </c>
+      <c r="E21" t="str">
+        <v>67.75</v>
+      </c>
+      <c r="F21" t="str">
+        <v>78.95</v>
+      </c>
+      <c r="G21" t="str">
+        <v>88.95</v>
+      </c>
+      <c r="H21" t="str">
+        <v>99.15</v>
+      </c>
+      <c r="I21" t="str">
+        <v>107.05</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>50</v>
+      </c>
+      <c r="B22" t="str">
+        <v>7.95</v>
+      </c>
+      <c r="C22" t="str">
+        <v>11.55</v>
+      </c>
+      <c r="D22" t="str">
+        <v>12.75</v>
+      </c>
+      <c r="E22" t="str">
+        <v>70.25</v>
+      </c>
+      <c r="F22" t="str">
+        <v>81.05</v>
+      </c>
+      <c r="G22" t="str">
+        <v>92.05</v>
+      </c>
+      <c r="H22" t="str">
+        <v>102.55</v>
+      </c>
+      <c r="I22" t="str">
+        <v>110.75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>60</v>
+      </c>
+      <c r="B23" t="str">
+        <v>8.05</v>
+      </c>
+      <c r="C23" t="str">
+        <v>11.75</v>
+      </c>
+      <c r="D23" t="str">
+        <v>12.95</v>
+      </c>
+      <c r="E23" t="str">
+        <v>74.95</v>
+      </c>
+      <c r="F23" t="str">
+        <v>86.45</v>
+      </c>
+      <c r="G23" t="str">
+        <v>98.15</v>
+      </c>
+      <c r="H23" t="str">
+        <v>109.35</v>
+      </c>
+      <c r="I23" t="str">
+        <v>118.15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>70</v>
+      </c>
+      <c r="B24" t="str">
+        <v>8.15</v>
+      </c>
+      <c r="C24" t="str">
+        <v>11.95</v>
+      </c>
+      <c r="D24" t="str">
+        <v>13.15</v>
+      </c>
+      <c r="E24" t="str">
+        <v>80.25</v>
+      </c>
+      <c r="F24" t="str">
+        <v>92.95</v>
+      </c>
+      <c r="G24" t="str">
+        <v>105.05</v>
+      </c>
+      <c r="H24" t="str">
+        <v>117.15</v>
+      </c>
+      <c r="I24" t="str">
+        <v>126.55</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>80</v>
+      </c>
+      <c r="B25" t="str">
+        <v>8.25</v>
+      </c>
+      <c r="C25" t="str">
+        <v>12.15</v>
+      </c>
+      <c r="D25" t="str">
+        <v>13.35</v>
+      </c>
+      <c r="E25" t="str">
+        <v>83.95</v>
+      </c>
+      <c r="F25" t="str">
+        <v>97.05</v>
+      </c>
+      <c r="G25" t="str">
+        <v>109.85</v>
+      </c>
+      <c r="H25" t="str">
+        <v>122.45</v>
+      </c>
+      <c r="I25" t="str">
+        <v>132.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>90</v>
+      </c>
+      <c r="B26" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="C26" t="str">
+        <v>12.35</v>
+      </c>
+      <c r="D26" t="str">
+        <v>13.55</v>
+      </c>
+      <c r="E26" t="str">
+        <v>93.25</v>
+      </c>
+      <c r="F26" t="str">
+        <v>107.45</v>
+      </c>
+      <c r="G26" t="str">
+        <v>122.05</v>
+      </c>
+      <c r="H26" t="str">
+        <v>136.05</v>
+      </c>
+      <c r="I26" t="str">
+        <v>146.95</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>100</v>
+      </c>
+      <c r="B27" t="str">
+        <v>8.45</v>
+      </c>
+      <c r="C27" t="str">
+        <v>12.55</v>
+      </c>
+      <c r="D27" t="str">
+        <v>13.75</v>
+      </c>
+      <c r="E27" t="str">
+        <v>106.55</v>
+      </c>
+      <c r="F27" t="str">
+        <v>123.95</v>
+      </c>
+      <c r="G27" t="str">
+        <v>139.55</v>
+      </c>
+      <c r="H27" t="str">
+        <v>155.55</v>
+      </c>
+      <c r="I27" t="str">
+        <v>167.95</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>125</v>
+      </c>
+      <c r="B28" t="str">
+        <v>8.55</v>
+      </c>
+      <c r="C28" t="str">
+        <v>12.75</v>
+      </c>
+      <c r="D28" t="str">
+        <v>13.95</v>
+      </c>
+      <c r="E28" t="str">
+        <v>119.25</v>
+      </c>
+      <c r="F28" t="str">
+        <v>138.05</v>
+      </c>
+      <c r="G28" t="str">
+        <v>156.05</v>
+      </c>
+      <c r="H28" t="str">
+        <v>173.95</v>
+      </c>
+      <c r="I28" t="str">
+        <v>187.95</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>150</v>
+      </c>
+      <c r="B29" t="str">
+        <v>8.65</v>
+      </c>
+      <c r="C29" t="str">
+        <v>12.75</v>
+      </c>
+      <c r="D29" t="str">
+        <v>14.15</v>
+      </c>
+      <c r="E29" t="str">
+        <v>126.55</v>
+      </c>
+      <c r="F29" t="str">
+        <v>146.15</v>
+      </c>
+      <c r="G29" t="str">
+        <v>165.65</v>
+      </c>
+      <c r="H29" t="str">
+        <v>184.65</v>
+      </c>
+      <c r="I29" t="str">
+        <v>199.45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>150+</v>
+      </c>
+      <c r="B30" t="str">
+        <v>8.75</v>
+      </c>
+      <c r="C30" t="str">
+        <v>12.95</v>
+      </c>
+      <c r="D30" t="str">
+        <v>14.35</v>
+      </c>
+      <c r="E30" t="str">
+        <v>166.15</v>
+      </c>
+      <c r="F30" t="str">
+        <v>192.45</v>
+      </c>
+      <c r="G30" t="str">
+        <v>217.55</v>
+      </c>
+      <c r="H30" t="str">
+        <v>242.55</v>
+      </c>
+      <c r="I30" t="str">
+        <v>261.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I30"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D30"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>x_min</v>
+      </c>
+      <c r="B1" t="str">
+        <v>x_max</v>
+      </c>
+      <c r="C1" t="str">
+        <v>value</v>
+      </c>
+      <c r="D1" t="str">
+        <v>remark</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>0</v>
+      </c>
+      <c r="B2" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="C2" t="str">
+        <v>12.35</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="C3" t="str">
+        <v>13.25</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="B4" t="str">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>13.85</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="C5" t="str">
+        <v>14.15</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2</v>
+      </c>
+      <c r="C6" t="str">
+        <v>14.45</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>3</v>
+      </c>
+      <c r="C7" t="str">
+        <v>15.75</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>4</v>
+      </c>
+      <c r="C8" t="str">
+        <v>17.05</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>5</v>
+      </c>
+      <c r="C9" t="str">
+        <v>18.45</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>6</v>
+      </c>
+      <c r="C10" t="str">
+        <v>25.45</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>6</v>
+      </c>
+      <c r="B11" t="str">
+        <v>7</v>
+      </c>
+      <c r="C11" t="str">
+        <v>27.05</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>7</v>
+      </c>
+      <c r="B12" t="str">
+        <v>8</v>
+      </c>
+      <c r="C12" t="str">
+        <v>28.85</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>9</v>
+      </c>
+      <c r="C13" t="str">
+        <v>29.65</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>9</v>
+      </c>
+      <c r="B14" t="str">
+        <v>11</v>
+      </c>
+      <c r="C14" t="str">
+        <v>41.25</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>11</v>
+      </c>
+      <c r="B15" t="str">
+        <v>13</v>
+      </c>
+      <c r="C15" t="str">
+        <v>42.15</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>15</v>
+      </c>
+      <c r="C16" t="str">
+        <v>45.05</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>15</v>
+      </c>
+      <c r="B17" t="str">
+        <v>17</v>
+      </c>
+      <c r="C17" t="str">
+        <v>48.55</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>20</v>
+      </c>
+      <c r="C18" t="str">
+        <v>54.75</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>20</v>
+      </c>
+      <c r="B19" t="str">
+        <v>25</v>
+      </c>
+      <c r="C19" t="str">
+        <v>64.05</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>25</v>
+      </c>
+      <c r="B20" t="str">
+        <v>30</v>
+      </c>
+      <c r="C20" t="str">
+        <v>65.95</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>30</v>
+      </c>
+      <c r="B21" t="str">
+        <v>40</v>
+      </c>
+      <c r="C21" t="str">
+        <v>67.75</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>40</v>
+      </c>
+      <c r="B22" t="str">
+        <v>50</v>
+      </c>
+      <c r="C22" t="str">
+        <v>70.25</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>50</v>
+      </c>
+      <c r="B23" t="str">
+        <v>60</v>
+      </c>
+      <c r="C23" t="str">
+        <v>74.95</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>60</v>
+      </c>
+      <c r="B24" t="str">
+        <v>70</v>
+      </c>
+      <c r="C24" t="str">
+        <v>80.25</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>70</v>
+      </c>
+      <c r="B25" t="str">
+        <v>80</v>
+      </c>
+      <c r="C25" t="str">
+        <v>83.95</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>80</v>
+      </c>
+      <c r="B26" t="str">
+        <v>90</v>
+      </c>
+      <c r="C26" t="str">
+        <v>93.25</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>90</v>
+      </c>
+      <c r="B27" t="str">
+        <v>100</v>
+      </c>
+      <c r="C27" t="str">
+        <v>106.55</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>100</v>
+      </c>
+      <c r="B28" t="str">
+        <v>125</v>
+      </c>
+      <c r="C28" t="str">
+        <v>119.25</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>125</v>
+      </c>
+      <c r="B29" t="str">
+        <v>150</v>
+      </c>
+      <c r="C29" t="str">
+        <v>126.55</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>150</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>166.15</v>
+      </c>
+      <c r="D30" t="str">
+        <v>150kg 以上</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>match_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>x_min</v>
+      </c>
+      <c r="C1" t="str">
+        <v>x_max</v>
+      </c>
+      <c r="D1" t="str">
+        <v>value</v>
+      </c>
+      <c r="E1" t="str">
+        <v>remark</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -537,22 +537,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
+        <v>巴西_美客多__item__1775655178925_d4gauu</v>
       </c>
       <c r="B3" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C3" t="str">
-        <v>汇损</v>
+        <v>活动费率</v>
       </c>
       <c r="D3" t="str">
         <v>number</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -564,18 +564,18 @@
         <v/>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>巴西_美客多__item__1775655178925_d4gauu</v>
+        <v>巴西_美客多__item__1775655178925_lj3exs</v>
       </c>
       <c r="B4" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C4" t="str">
-        <v>活动费率</v>
+        <v>折扣</v>
       </c>
       <c r="D4" t="str">
         <v>number</v>
@@ -596,27 +596,27 @@
         <v/>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
+        <v>巴西_美客多__item__1775655178925_qfbetw</v>
       </c>
       <c r="B5" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C5" t="str">
-        <v>活动费率</v>
+        <v>提现费率</v>
       </c>
       <c r="D5" t="str">
         <v>number</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -628,18 +628,18 @@
         <v/>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>巴西_美客多__item__1775655178925_lj3exs</v>
+        <v>巴西_美客多__item__1775655178925_ta67tt</v>
       </c>
       <c r="B6" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C6" t="str">
-        <v>折扣</v>
+        <v>交易费率</v>
       </c>
       <c r="D6" t="str">
         <v>number</v>
@@ -660,27 +660,27 @@
         <v/>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
+        <v>巴西_美客多__item__1775655178925_18be97</v>
       </c>
       <c r="B7" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C7" t="str">
-        <v>折扣</v>
+        <v>汇率</v>
       </c>
       <c r="D7" t="str">
         <v>number</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -692,18 +692,18 @@
         <v/>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>巴西_美客多__item__1775655178925_qfbetw</v>
+        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
       </c>
       <c r="B8" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C8" t="str">
-        <v>提现费率</v>
+        <v>税率</v>
       </c>
       <c r="D8" t="str">
         <v>number</v>
@@ -724,27 +724,27 @@
         <v/>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
+        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
       </c>
       <c r="B9" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C9" t="str">
-        <v>提现费率</v>
+        <v>贴单费用</v>
       </c>
       <c r="D9" t="str">
         <v>number</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>R$</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -756,27 +756,27 @@
         <v/>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>巴西_美客多__item__1775655178925_ta67tt</v>
+        <v>巴西_美客多__item__1775655178925_4tnm24</v>
       </c>
       <c r="B10" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C10" t="str">
-        <v>交易费率</v>
+        <v>是否包邮</v>
       </c>
       <c r="D10" t="str">
-        <v>number</v>
+        <v>boolean</v>
       </c>
       <c r="E10" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>2</v>
+        <v>是</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -788,114 +788,114 @@
         <v/>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>巴西_TikTok__item__1775655438790_two67j</v>
+        <v>巴西_美客多__item__seller_shipping</v>
       </c>
       <c r="B11" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C11" t="str">
-        <v>交易费率</v>
+        <v>卖家支付运费</v>
       </c>
       <c r="D11" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>R$</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>if({是否包邮} == "是", 0, 查表("巴西美客多运费补贴表", {折后售价}, {重量}))</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>condition</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>ml_br_shipping_fee</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>{"field":"是否包邮","operator":"eq","compareValue":"是","thenAction":{"kind":"fixed","value":"0","tableId":"","args":[]},"elseAction":{"kind":"table","value":"","tableId":"ml_br_shipping_fee","args":["折后售价","重量"]}}</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>巴西_美客多__item__1775655178925_18be97</v>
+        <v>巴西_美客多__item__commission_rate</v>
       </c>
       <c r="B12" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C12" t="str">
-        <v>汇率</v>
+        <v>佣金费率</v>
       </c>
       <c r="D12" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E12" t="str">
         <v>%</v>
       </c>
       <c r="F12" t="str">
-        <v>2</v>
+        <v>查表("巴西美客多佣金表", {类目}, {广告类型})</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>advanced</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>ml_br_commission</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>{"expression":"查表(\"巴西美客多佣金表\", {类目}, {广告类型})"}</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
+        <v>巴西_美客多__item__fixed_surcharge</v>
       </c>
       <c r="B13" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C13" t="str">
-        <v>汇率</v>
+        <v>固定附加费</v>
       </c>
       <c r="D13" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>R$</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表("巴西美客多固定附加费表", {折后售价}))</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>advanced</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>ml_br_fixed_fee</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>{"expression":"if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表(\"巴西美客多固定附加费表\", {折后售价}))"}</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
+        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
       </c>
       <c r="B14" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C14" t="str">
-        <v>税率</v>
+        <v>汇损</v>
       </c>
       <c r="D14" t="str">
         <v>number</v>
@@ -904,7 +904,7 @@
         <v>%</v>
       </c>
       <c r="F14" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -913,30 +913,30 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>巴西_TikTok__item__1775655438790_swod7s</v>
+        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
       </c>
       <c r="B15" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C15" t="str">
-        <v>税率</v>
+        <v>活动费率</v>
       </c>
       <c r="D15" t="str">
         <v>number</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -945,30 +945,30 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
+        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
       </c>
       <c r="B16" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C16" t="str">
-        <v>贴单费用</v>
+        <v>折扣</v>
       </c>
       <c r="D16" t="str">
         <v>number</v>
       </c>
       <c r="E16" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F16" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -977,30 +977,30 @@
         <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
+        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
       </c>
       <c r="B17" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C17" t="str">
-        <v>贴单费用</v>
+        <v>提现费率</v>
       </c>
       <c r="D17" t="str">
         <v>number</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1009,30 +1009,30 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>巴西_美客多__item__1775655178925_4tnm24</v>
+        <v>巴西_TikTok__item__1775655438790_two67j</v>
       </c>
       <c r="B18" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C18" t="str">
-        <v>是否包邮</v>
+        <v>交易费率</v>
       </c>
       <c r="D18" t="str">
-        <v>boolean</v>
+        <v>number</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F18" t="str">
-        <v>是</v>
+        <v>3</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1041,30 +1041,30 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J18">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>巴西_TikTok__item__1775655438790_dpk097</v>
+        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
       </c>
       <c r="B19" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C19" t="str">
-        <v>是否包邮</v>
+        <v>汇率</v>
       </c>
       <c r="D19" t="str">
-        <v>boolean</v>
+        <v>number</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F19" t="str">
-        <v>是</v>
+        <v>3</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1073,106 +1073,106 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J19">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>巴西_美客多__item__seller_shipping</v>
+        <v>巴西_TikTok__item__1775655438790_swod7s</v>
       </c>
       <c r="B20" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C20" t="str">
-        <v>卖家支付运费</v>
+        <v>税率</v>
       </c>
       <c r="D20" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E20" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F20" t="str">
-        <v>if({是否包邮} == "是", 0, 查表("巴西美客多运费补贴表", {折后售价}, {重量}))</v>
+        <v>3</v>
       </c>
       <c r="G20" t="str">
-        <v>condition</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>ml_br_shipping_fee</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>{"field":"是否包邮","operator":"eq","compareValue":"是","thenAction":{"kind":"fixed","value":"0","tableId":"","args":[]},"elseAction":{"kind":"table","value":"","tableId":"ml_br_shipping_fee","args":["折后售价","重量"]}}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J20">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>巴西_美客多__item__commission_rate</v>
+        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
       </c>
       <c r="B21" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C21" t="str">
-        <v>佣金费率</v>
+        <v>贴单费用</v>
       </c>
       <c r="D21" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E21" t="str">
-        <v>%</v>
+        <v>R$</v>
       </c>
       <c r="F21" t="str">
-        <v>查表("巴西美客多佣金表", {类目}, {广告类型})</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str">
-        <v>advanced</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>ml_br_commission</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>{"expression":"查表(\"巴西美客多佣金表\", {类目}, {广告类型})"}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J21">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>巴西_美客多__item__fixed_surcharge</v>
+        <v>巴西_TikTok__item__1775655438790_dpk097</v>
       </c>
       <c r="B22" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C22" t="str">
-        <v>固定附加费</v>
+        <v>是否包邮</v>
       </c>
       <c r="D22" t="str">
-        <v>rule</v>
+        <v>boolean</v>
       </c>
       <c r="E22" t="str">
-        <v>R$</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表("巴西美客多固定附加费表", {折后售价}))</v>
+        <v>是</v>
       </c>
       <c r="G22" t="str">
-        <v>advanced</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>ml_br_fixed_fee</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>{"expression":"if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表(\"巴西美客多固定附加费表\", {折后售价}))"}</v>
+        <v/>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -520,7 +520,7 @@
         <v>%</v>
       </c>
       <c r="F2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -529,7 +529,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -552,7 +552,7 @@
         <v>%</v>
       </c>
       <c r="F3" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -561,7 +561,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -584,7 +584,7 @@
         <v>%</v>
       </c>
       <c r="F4" t="str">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -593,7 +593,7 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -616,7 +616,7 @@
         <v>%</v>
       </c>
       <c r="F5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -625,7 +625,7 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -680,7 +680,7 @@
         <v>%</v>
       </c>
       <c r="F7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -689,7 +689,7 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J7">
         <v>6</v>

--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -10,6 +10,8 @@
     <sheet name="tpl_ml_br_shipping_fee" sheetId="5" r:id="rId5"/>
     <sheet name="tpl_ml_br_ship_fast_79" sheetId="6" r:id="rId6"/>
     <sheet name="tpl_ml_br_commission" sheetId="7" r:id="rId7"/>
+    <sheet name="app_options" sheetId="8" r:id="rId8"/>
+    <sheet name="app_option_groups" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -537,13 +539,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>巴西_美客多__item__1775655178925_d4gauu</v>
+        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
       </c>
       <c r="B3" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C3" t="str">
-        <v>活动费率</v>
+        <v>汇损</v>
       </c>
       <c r="D3" t="str">
         <v>number</v>
@@ -552,7 +554,7 @@
         <v>%</v>
       </c>
       <c r="F3" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -564,18 +566,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>巴西_美客多__item__1775655178925_lj3exs</v>
+        <v>巴西_美客多__item__1775655178925_d4gauu</v>
       </c>
       <c r="B4" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C4" t="str">
-        <v>折扣</v>
+        <v>活动费率</v>
       </c>
       <c r="D4" t="str">
         <v>number</v>
@@ -584,7 +586,7 @@
         <v>%</v>
       </c>
       <c r="F4" t="str">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -596,18 +598,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>巴西_美客多__item__1775655178925_qfbetw</v>
+        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
       </c>
       <c r="B5" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C5" t="str">
-        <v>提现费率</v>
+        <v>活动费率</v>
       </c>
       <c r="D5" t="str">
         <v>number</v>
@@ -616,7 +618,7 @@
         <v>%</v>
       </c>
       <c r="F5" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -628,18 +630,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>巴西_美客多__item__1775655178925_ta67tt</v>
+        <v>巴西_美客多__item__1775655178925_lj3exs</v>
       </c>
       <c r="B6" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C6" t="str">
-        <v>交易费率</v>
+        <v>折扣</v>
       </c>
       <c r="D6" t="str">
         <v>number</v>
@@ -648,7 +650,7 @@
         <v>%</v>
       </c>
       <c r="F6" t="str">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -657,21 +659,21 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>巴西_美客多__item__1775655178925_18be97</v>
+        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
       </c>
       <c r="B7" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C7" t="str">
-        <v>汇率</v>
+        <v>折扣</v>
       </c>
       <c r="D7" t="str">
         <v>number</v>
@@ -680,7 +682,7 @@
         <v>%</v>
       </c>
       <c r="F7" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -692,18 +694,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
+        <v>巴西_美客多__item__1775655178925_qfbetw</v>
       </c>
       <c r="B8" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C8" t="str">
-        <v>税率</v>
+        <v>提现费率</v>
       </c>
       <c r="D8" t="str">
         <v>number</v>
@@ -712,7 +714,7 @@
         <v>%</v>
       </c>
       <c r="F8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -721,30 +723,30 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
+        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
       </c>
       <c r="B9" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C9" t="str">
-        <v>贴单费用</v>
+        <v>提现费率</v>
       </c>
       <c r="D9" t="str">
         <v>number</v>
       </c>
       <c r="E9" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F9" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -753,30 +755,30 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>巴西_美客多__item__1775655178925_4tnm24</v>
+        <v>巴西_美客多__item__1775655178925_ta67tt</v>
       </c>
       <c r="B10" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C10" t="str">
-        <v>是否包邮</v>
+        <v>交易费率</v>
       </c>
       <c r="D10" t="str">
-        <v>boolean</v>
+        <v>number</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F10" t="str">
-        <v>是</v>
+        <v>2</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -788,114 +790,114 @@
         <v/>
       </c>
       <c r="J10">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>巴西_美客多__item__seller_shipping</v>
+        <v>巴西_TikTok__item__1775655438790_two67j</v>
       </c>
       <c r="B11" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C11" t="str">
-        <v>卖家支付运费</v>
+        <v>交易费率</v>
       </c>
       <c r="D11" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E11" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F11" t="str">
-        <v>if({是否包邮} == "是", 0, 查表("巴西美客多运费补贴表", {折后售价}, {重量}))</v>
+        <v>3</v>
       </c>
       <c r="G11" t="str">
-        <v>condition</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>ml_br_shipping_fee</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>{"field":"是否包邮","operator":"eq","compareValue":"是","thenAction":{"kind":"fixed","value":"0","tableId":"","args":[]},"elseAction":{"kind":"table","value":"","tableId":"ml_br_shipping_fee","args":["折后售价","重量"]}}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>巴西_美客多__item__commission_rate</v>
+        <v>巴西_美客多__item__1775655178925_18be97</v>
       </c>
       <c r="B12" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C12" t="str">
-        <v>佣金费率</v>
+        <v>汇率</v>
       </c>
       <c r="D12" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E12" t="str">
         <v>%</v>
       </c>
       <c r="F12" t="str">
-        <v>查表("巴西美客多佣金表", {类目}, {广告类型})</v>
+        <v>1</v>
       </c>
       <c r="G12" t="str">
-        <v>advanced</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>ml_br_commission</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>{"expression":"查表(\"巴西美客多佣金表\", {类目}, {广告类型})"}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>巴西_美客多__item__fixed_surcharge</v>
+        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
       </c>
       <c r="B13" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C13" t="str">
-        <v>固定附加费</v>
+        <v>汇率</v>
       </c>
       <c r="D13" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E13" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F13" t="str">
-        <v>if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表("巴西美客多固定附加费表", {折后售价}))</v>
+        <v>3</v>
       </c>
       <c r="G13" t="str">
-        <v>advanced</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>ml_br_fixed_fee</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>{"expression":"if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表(\"巴西美客多固定附加费表\", {折后售价}))"}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J13">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
+        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
       </c>
       <c r="B14" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C14" t="str">
-        <v>汇损</v>
+        <v>税率</v>
       </c>
       <c r="D14" t="str">
         <v>number</v>
@@ -904,7 +906,7 @@
         <v>%</v>
       </c>
       <c r="F14" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -913,21 +915,21 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v/>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
+        <v>巴西_TikTok__item__1775655438790_swod7s</v>
       </c>
       <c r="B15" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C15" t="str">
-        <v>活动费率</v>
+        <v>税率</v>
       </c>
       <c r="D15" t="str">
         <v>number</v>
@@ -948,27 +950,27 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
+        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
       </c>
       <c r="B16" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C16" t="str">
-        <v>折扣</v>
+        <v>贴单费用</v>
       </c>
       <c r="D16" t="str">
         <v>number</v>
       </c>
       <c r="E16" t="str">
-        <v>%</v>
+        <v>R$</v>
       </c>
       <c r="F16" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -977,27 +979,27 @@
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v/>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
+        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
       </c>
       <c r="B17" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C17" t="str">
-        <v>提现费率</v>
+        <v>贴单费用</v>
       </c>
       <c r="D17" t="str">
         <v>number</v>
       </c>
       <c r="E17" t="str">
-        <v>%</v>
+        <v>R$</v>
       </c>
       <c r="F17" t="str">
         <v>3</v>
@@ -1012,27 +1014,27 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>巴西_TikTok__item__1775655438790_two67j</v>
+        <v>巴西_美客多__item__1775655178925_4tnm24</v>
       </c>
       <c r="B18" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C18" t="str">
-        <v>交易费率</v>
+        <v>是否包邮</v>
       </c>
       <c r="D18" t="str">
-        <v>number</v>
+        <v>boolean</v>
       </c>
       <c r="E18" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>3</v>
+        <v>是</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1041,30 +1043,30 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v/>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
+        <v>巴西_TikTok__item__1775655438790_dpk097</v>
       </c>
       <c r="B19" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C19" t="str">
-        <v>汇率</v>
+        <v>是否包邮</v>
       </c>
       <c r="D19" t="str">
-        <v>number</v>
+        <v>boolean</v>
       </c>
       <c r="E19" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>3</v>
+        <v>是</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1073,106 +1075,106 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v/>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>巴西_TikTok__item__1775655438790_swod7s</v>
+        <v>巴西_美客多__item__seller_shipping</v>
       </c>
       <c r="B20" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C20" t="str">
-        <v>税率</v>
+        <v>卖家支付运费</v>
       </c>
       <c r="D20" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E20" t="str">
-        <v>%</v>
+        <v>R$</v>
       </c>
       <c r="F20" t="str">
-        <v>3</v>
+        <v>if({是否包邮} == "是", 0, 查表("巴西美客多运费补贴表", {折后售价}, {重量}))</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>condition</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>ml_br_shipping_fee</v>
       </c>
       <c r="I20" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v>{"field":"是否包邮","operator":"eq","compareValue":"是","thenAction":{"kind":"fixed","value":"0","tableId":"","args":[]},"elseAction":{"kind":"table","value":"","tableId":"ml_br_shipping_fee","args":["折后售价","重量"]}}</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
+        <v>巴西_美客多__item__commission_rate</v>
       </c>
       <c r="B21" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C21" t="str">
-        <v>贴单费用</v>
+        <v>佣金费率</v>
       </c>
       <c r="D21" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E21" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F21" t="str">
-        <v>3</v>
+        <v>查表("巴西美客多佣金表", {类目}, {广告类型})</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>advanced</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>ml_br_commission</v>
       </c>
       <c r="I21" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v>{"expression":"查表(\"巴西美客多佣金表\", {类目}, {广告类型})"}</v>
       </c>
       <c r="J21">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>巴西_TikTok__item__1775655438790_dpk097</v>
+        <v>巴西_美客多__item__fixed_surcharge</v>
       </c>
       <c r="B22" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C22" t="str">
-        <v>是否包邮</v>
+        <v>固定附加费</v>
       </c>
       <c r="D22" t="str">
-        <v>boolean</v>
+        <v>rule</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>R$</v>
       </c>
       <c r="F22" t="str">
-        <v>是</v>
+        <v>if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表("巴西美客多固定附加费表", {折后售价}))</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>advanced</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>ml_br_fixed_fee</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>{"expression":"if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表(\"巴西美客多固定附加费表\", {折后售价}))"}</v>
       </c>
       <c r="J22">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1361,7 +1363,7 @@
         <v>tpl_ml_br_commission</v>
       </c>
       <c r="D5" t="str">
-        <v>enum_range</v>
+        <v>enum_pair</v>
       </c>
       <c r="E5" t="str">
         <v>巴西</v>
@@ -2779,45 +2781,385 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>match_key</v>
       </c>
       <c r="B1" t="str">
-        <v>x_min</v>
+        <v>match_key_2</v>
       </c>
       <c r="C1" t="str">
-        <v>x_max</v>
+        <v>value</v>
+      </c>
+      <c r="D1" t="str">
+        <v>remark</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v>Clássico</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>填写该类目在 Mercado Livre 后台查询到的精确费率。</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v>Premium</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>填写该类目在 Mercado Livre 后台查询到的精确费率。</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>group_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>label</v>
       </c>
       <c r="D1" t="str">
         <v>value</v>
       </c>
       <c r="E1" t="str">
+        <v>sort</v>
+      </c>
+      <c r="F1" t="str">
+        <v>enabled</v>
+      </c>
+      <c r="G1" t="str">
         <v>remark</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>shipping_included__yes</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>shipping_included</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
+        <v>是</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>默认包邮。</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>shipping_included__no</v>
+      </c>
+      <c r="B3" t="str">
+        <v>shipping_included</v>
+      </c>
+      <c r="C3" t="str">
+        <v>否</v>
+      </c>
+      <c r="D3" t="str">
+        <v>否</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
+        <v>非包邮。</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ad_type__classico</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ad_type</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Clássico</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Clássico</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Mercado Livre 广告类型。</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ad_type__premium</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ad_type</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Premium</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Premium</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Mercado Livre 广告类型。</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>category__default</v>
+      </c>
+      <c r="B6" t="str">
+        <v>category</v>
+      </c>
+      <c r="C6" t="str">
+        <v>默认</v>
+      </c>
+      <c r="D6" t="str">
+        <v>默认</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>category__fashion</v>
+      </c>
+      <c r="B7" t="str">
+        <v>category</v>
+      </c>
+      <c r="C7" t="str">
+        <v>服饰</v>
+      </c>
+      <c r="D7" t="str">
+        <v>服饰</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>category__3c</v>
+      </c>
+      <c r="B8" t="str">
+        <v>category</v>
+      </c>
+      <c r="C8" t="str">
+        <v>3C</v>
+      </c>
+      <c r="D8" t="str">
+        <v>3C</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>category__home</v>
+      </c>
+      <c r="B9" t="str">
+        <v>category</v>
+      </c>
+      <c r="C9" t="str">
+        <v>家居</v>
+      </c>
+      <c r="D9" t="str">
+        <v>家居</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>category__beauty</v>
+      </c>
+      <c r="B10" t="str">
+        <v>category</v>
+      </c>
+      <c r="C10" t="str">
+        <v>美妆</v>
+      </c>
+      <c r="D10" t="str">
+        <v>美妆</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>sort</v>
+      </c>
+      <c r="E1" t="str">
+        <v>enabled</v>
+      </c>
+      <c r="F1" t="str">
+        <v>remark</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ad_type</v>
+      </c>
+      <c r="B2" t="str">
+        <v>广告类型</v>
+      </c>
+      <c r="C2" t="str">
+        <v>创建页和佣金表里使用的广告类型选项。</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>category</v>
+      </c>
+      <c r="B3" t="str">
+        <v>类目</v>
+      </c>
+      <c r="C3" t="str">
+        <v>创建页和佣金表里使用的类目选项。</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>shipping_included</v>
+      </c>
+      <c r="B4" t="str">
+        <v>是否包邮</v>
+      </c>
+      <c r="C4" t="str">
+        <v>创建页当前包邮状态使用的选项。</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -12,6 +12,7 @@
     <sheet name="tpl_ml_br_commission" sheetId="7" r:id="rId7"/>
     <sheet name="app_options" sheetId="8" r:id="rId8"/>
     <sheet name="app_option_groups" sheetId="9" r:id="rId9"/>
+    <sheet name="tpl_table_1776352156329_r4sw82" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -469,9 +470,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>match_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>match_key_2</v>
+      </c>
+      <c r="C1" t="str">
+        <v>value</v>
+      </c>
+      <c r="D1" t="str">
+        <v>remark</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -539,13 +579,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
+        <v>巴西_美客多__item__1775655178925_d4gauu</v>
       </c>
       <c r="B3" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C3" t="str">
-        <v>汇损</v>
+        <v>活动费率</v>
       </c>
       <c r="D3" t="str">
         <v>number</v>
@@ -554,7 +594,7 @@
         <v>%</v>
       </c>
       <c r="F3" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -566,18 +606,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>巴西_美客多__item__1775655178925_d4gauu</v>
+        <v>巴西_美客多__item__1775655178925_lj3exs</v>
       </c>
       <c r="B4" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C4" t="str">
-        <v>活动费率</v>
+        <v>折扣</v>
       </c>
       <c r="D4" t="str">
         <v>number</v>
@@ -586,7 +626,7 @@
         <v>%</v>
       </c>
       <c r="F4" t="str">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -598,18 +638,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
+        <v>巴西_美客多__item__1775655178925_qfbetw</v>
       </c>
       <c r="B5" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C5" t="str">
-        <v>活动费率</v>
+        <v>提现费率</v>
       </c>
       <c r="D5" t="str">
         <v>number</v>
@@ -618,7 +658,7 @@
         <v>%</v>
       </c>
       <c r="F5" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -630,18 +670,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>巴西_美客多__item__1775655178925_lj3exs</v>
+        <v>巴西_美客多__item__1775655178925_ta67tt</v>
       </c>
       <c r="B6" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C6" t="str">
-        <v>折扣</v>
+        <v>交易费率</v>
       </c>
       <c r="D6" t="str">
         <v>number</v>
@@ -650,7 +690,7 @@
         <v>%</v>
       </c>
       <c r="F6" t="str">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -659,21 +699,21 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v/>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
+        <v>巴西_美客多__item__1775655178925_18be97</v>
       </c>
       <c r="B7" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C7" t="str">
-        <v>折扣</v>
+        <v>汇率</v>
       </c>
       <c r="D7" t="str">
         <v>number</v>
@@ -682,7 +722,7 @@
         <v>%</v>
       </c>
       <c r="F7" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -694,18 +734,18 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>巴西_美客多__item__1775655178925_qfbetw</v>
+        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
       </c>
       <c r="B8" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C8" t="str">
-        <v>提现费率</v>
+        <v>税率</v>
       </c>
       <c r="D8" t="str">
         <v>number</v>
@@ -714,7 +754,7 @@
         <v>%</v>
       </c>
       <c r="F8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -723,30 +763,30 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v/>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
+        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
       </c>
       <c r="B9" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C9" t="str">
-        <v>提现费率</v>
+        <v>贴单费用</v>
       </c>
       <c r="D9" t="str">
         <v>number</v>
       </c>
       <c r="E9" t="str">
-        <v>%</v>
+        <v>R$</v>
       </c>
       <c r="F9" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -755,30 +795,30 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v/>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>巴西_美客多__item__1775655178925_ta67tt</v>
+        <v>巴西_美客多__item__1775655178925_4tnm24</v>
       </c>
       <c r="B10" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C10" t="str">
-        <v>交易费率</v>
+        <v>是否包邮</v>
       </c>
       <c r="D10" t="str">
-        <v>number</v>
+        <v>boolean</v>
       </c>
       <c r="E10" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>2</v>
+        <v>是</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -790,123 +830,123 @@
         <v/>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>巴西_TikTok__item__1775655438790_two67j</v>
+        <v>巴西_美客多__item__seller_shipping</v>
       </c>
       <c r="B11" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C11" t="str">
-        <v>交易费率</v>
+        <v>卖家支付运费</v>
       </c>
       <c r="D11" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E11" t="str">
-        <v>%</v>
+        <v>R$</v>
       </c>
       <c r="F11" t="str">
-        <v>3</v>
+        <v>if({是否包邮} == "是", 0, 查表("巴西美客多运费补贴表", {折后售价}, {重量}))</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>condition</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>ml_br_shipping_fee</v>
       </c>
       <c r="I11" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v>{"field":"是否包邮","operator":"eq","compareValue":"是","thenAction":{"kind":"fixed","value":"0","tableId":"","args":[]},"elseAction":{"kind":"table","value":"","tableId":"ml_br_shipping_fee","args":["折后售价","重量"]}}</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>巴西_美客多__item__1775655178925_18be97</v>
+        <v>巴西_美客多__item__commission_rate</v>
       </c>
       <c r="B12" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C12" t="str">
-        <v>汇率</v>
+        <v>佣金费率</v>
       </c>
       <c r="D12" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E12" t="str">
         <v>%</v>
       </c>
       <c r="F12" t="str">
-        <v>1</v>
+        <v>查表("巴西美客多佣金表", {类目}, {广告类型})</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>advanced</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>ml_br_commission</v>
       </c>
       <c r="I12" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v>{"expression":"查表(\"巴西美客多佣金表\", {类目}, {广告类型})"}</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
+        <v>巴西_美客多__item__fixed_surcharge</v>
       </c>
       <c r="B13" t="str">
-        <v>巴西_TikTok</v>
+        <v>巴西_美客多</v>
       </c>
       <c r="C13" t="str">
-        <v>汇率</v>
+        <v>固定附加费</v>
       </c>
       <c r="D13" t="str">
-        <v>number</v>
+        <v>rule</v>
       </c>
       <c r="E13" t="str">
-        <v>%</v>
+        <v>R$</v>
       </c>
       <c r="F13" t="str">
-        <v>3</v>
+        <v>if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表("巴西美客多固定附加费表", {折后售价}))</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>advanced</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>ml_br_fixed_fee</v>
       </c>
       <c r="I13" t="str">
-        <v>{"tableId":"","args":[]}</v>
+        <v>{"expression":"if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表(\"巴西美客多固定附加费表\", {折后售价}))"}</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>巴西_美客多__item__1775655178925_h0k0pj</v>
+        <v>巴西_美客多__item__1776349376092_on03oz</v>
       </c>
       <c r="B14" t="str">
         <v>巴西_美客多</v>
       </c>
       <c r="C14" t="str">
-        <v>税率</v>
+        <v>类目</v>
       </c>
       <c r="D14" t="str">
         <v>number</v>
       </c>
       <c r="E14" t="str">
-        <v>%</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>2</v>
+        <v>默认</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -915,21 +955,21 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>巴西_TikTok__item__1775655438790_swod7s</v>
+        <v>巴西_TikTok__item__1775655438790_7uh4ba</v>
       </c>
       <c r="B15" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C15" t="str">
-        <v>税率</v>
+        <v>汇损</v>
       </c>
       <c r="D15" t="str">
         <v>number</v>
@@ -950,56 +990,56 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>巴西_美客多__item__1775655178925_0kxg8t</v>
+        <v>巴西_TikTok__item__1775655438790_wrzw18</v>
       </c>
       <c r="B16" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C16" t="str">
-        <v>贴单费用</v>
+        <v>活动费率</v>
       </c>
       <c r="D16" t="str">
         <v>number</v>
       </c>
       <c r="E16" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F16" t="str">
+        <v>3</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>{"tableId":"","args":[]}</v>
+      </c>
+      <c r="J16">
         <v>2</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16">
-        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
+        <v>巴西_TikTok__item__1775655438790_rmhk48</v>
       </c>
       <c r="B17" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C17" t="str">
-        <v>贴单费用</v>
+        <v>折扣</v>
       </c>
       <c r="D17" t="str">
         <v>number</v>
       </c>
       <c r="E17" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F17" t="str">
         <v>3</v>
@@ -1014,27 +1054,27 @@
         <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>巴西_美客多__item__1775655178925_4tnm24</v>
+        <v>巴西_TikTok__item__1775655438790_vcr0y5</v>
       </c>
       <c r="B18" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C18" t="str">
-        <v>是否包邮</v>
+        <v>提现费率</v>
       </c>
       <c r="D18" t="str">
-        <v>boolean</v>
+        <v>number</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F18" t="str">
-        <v>是</v>
+        <v>3</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1043,30 +1083,30 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J18">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>巴西_TikTok__item__1775655438790_dpk097</v>
+        <v>巴西_TikTok__item__1775655438790_two67j</v>
       </c>
       <c r="B19" t="str">
         <v>巴西_TikTok</v>
       </c>
       <c r="C19" t="str">
-        <v>是否包邮</v>
+        <v>交易费率</v>
       </c>
       <c r="D19" t="str">
-        <v>boolean</v>
+        <v>number</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>%</v>
       </c>
       <c r="F19" t="str">
-        <v>是</v>
+        <v>3</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1075,118 +1115,150 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J19">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>巴西_美客多__item__seller_shipping</v>
+        <v>巴西_TikTok__item__1775655438790_kxal2h</v>
       </c>
       <c r="B20" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C20" t="str">
-        <v>卖家支付运费</v>
+        <v>汇率</v>
       </c>
       <c r="D20" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E20" t="str">
-        <v>R$</v>
+        <v>%</v>
       </c>
       <c r="F20" t="str">
-        <v>if({是否包邮} == "是", 0, 查表("巴西美客多运费补贴表", {折后售价}, {重量}))</v>
+        <v>3</v>
       </c>
       <c r="G20" t="str">
-        <v>condition</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>ml_br_shipping_fee</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>{"field":"是否包邮","operator":"eq","compareValue":"是","thenAction":{"kind":"fixed","value":"0","tableId":"","args":[]},"elseAction":{"kind":"table","value":"","tableId":"ml_br_shipping_fee","args":["折后售价","重量"]}}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J20">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>巴西_美客多__item__commission_rate</v>
+        <v>巴西_TikTok__item__1775655438790_swod7s</v>
       </c>
       <c r="B21" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C21" t="str">
-        <v>佣金费率</v>
+        <v>税率</v>
       </c>
       <c r="D21" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E21" t="str">
         <v>%</v>
       </c>
       <c r="F21" t="str">
-        <v>查表("巴西美客多佣金表", {类目}, {广告类型})</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str">
-        <v>advanced</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>ml_br_commission</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>{"expression":"查表(\"巴西美客多佣金表\", {类目}, {广告类型})"}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J21">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>巴西_美客多__item__fixed_surcharge</v>
+        <v>巴西_TikTok__item__1775655438790_0j5ef4</v>
       </c>
       <c r="B22" t="str">
-        <v>巴西_美客多</v>
+        <v>巴西_TikTok</v>
       </c>
       <c r="C22" t="str">
-        <v>固定附加费</v>
+        <v>贴单费用</v>
       </c>
       <c r="D22" t="str">
-        <v>rule</v>
+        <v>number</v>
       </c>
       <c r="E22" t="str">
         <v>R$</v>
       </c>
       <c r="F22" t="str">
-        <v>if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表("巴西美客多固定附加费表", {折后售价}))</v>
+        <v>3</v>
       </c>
       <c r="G22" t="str">
-        <v>advanced</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>ml_br_fixed_fee</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>{"expression":"if({折后售价} &lt; 12.5, {折后售价} * 0.5, 查表(\"巴西美客多固定附加费表\", {折后售价}))"}</v>
+        <v>{"tableId":"","args":[]}</v>
       </c>
       <c r="J22">
-        <v>12</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>巴西_TikTok__item__1775655438790_dpk097</v>
+      </c>
+      <c r="B23" t="str">
+        <v>巴西_TikTok</v>
+      </c>
+      <c r="C23" t="str">
+        <v>是否包邮</v>
+      </c>
+      <c r="D23" t="str">
+        <v>boolean</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>是</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1393,9 +1465,50 @@
         <v>来源页当前只明确给出费率范围：Clássico 为 10%~14%，Premium 为 15%~19%。类目细表未直接给出，这里先不写死猜测值。</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B6" t="str">
+        <v>未命名规则表 5</v>
+      </c>
+      <c r="C6" t="str">
+        <v>tpl_table_1776352156329_r4sw82</v>
+      </c>
+      <c r="D6" t="str">
+        <v>enum_pair</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2861,16 +2974,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>shipping_included__yes</v>
+        <v>ad_type__classico</v>
       </c>
       <c r="B2" t="str">
-        <v>shipping_included</v>
+        <v>ad_type</v>
       </c>
       <c r="C2" t="str">
-        <v>是</v>
+        <v>Clássico</v>
       </c>
       <c r="D2" t="str">
-        <v>是</v>
+        <v>Clássico</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2879,21 +2992,21 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>默认包邮。</v>
+        <v>Mercado Livre 广告类型。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>shipping_included__no</v>
+        <v>ad_type__premium</v>
       </c>
       <c r="B3" t="str">
-        <v>shipping_included</v>
+        <v>ad_type</v>
       </c>
       <c r="C3" t="str">
-        <v>否</v>
+        <v>Premium</v>
       </c>
       <c r="D3" t="str">
-        <v>否</v>
+        <v>Premium</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2902,21 +3015,21 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>非包邮。</v>
+        <v>Mercado Livre 广告类型。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ad_type__classico</v>
+        <v>category__default</v>
       </c>
       <c r="B4" t="str">
-        <v>ad_type</v>
+        <v>category</v>
       </c>
       <c r="C4" t="str">
-        <v>Clássico</v>
+        <v>默认</v>
       </c>
       <c r="D4" t="str">
-        <v>Clássico</v>
+        <v>默认</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2925,47 +3038,47 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>Mercado Livre 广告类型。</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ad_type__premium</v>
+        <v>category__fashion</v>
       </c>
       <c r="B5" t="str">
-        <v>ad_type</v>
+        <v>category</v>
       </c>
       <c r="C5" t="str">
-        <v>Premium</v>
+        <v>服饰</v>
       </c>
       <c r="D5" t="str">
-        <v>Premium</v>
+        <v>服饰</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>Mercado Livre 广告类型。</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>category__default</v>
+        <v>category__3c</v>
       </c>
       <c r="B6" t="str">
         <v>category</v>
       </c>
       <c r="C6" t="str">
-        <v>默认</v>
+        <v>3C</v>
       </c>
       <c r="D6" t="str">
-        <v>默认</v>
+        <v>3C</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2976,19 +3089,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>category__fashion</v>
+        <v>category__home</v>
       </c>
       <c r="B7" t="str">
         <v>category</v>
       </c>
       <c r="C7" t="str">
-        <v>服饰</v>
+        <v>家居</v>
       </c>
       <c r="D7" t="str">
-        <v>服饰</v>
+        <v>家居</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2999,19 +3112,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>category__3c</v>
+        <v>category__beauty</v>
       </c>
       <c r="B8" t="str">
         <v>category</v>
       </c>
       <c r="C8" t="str">
-        <v>3C</v>
+        <v>美妆</v>
       </c>
       <c r="D8" t="str">
-        <v>3C</v>
+        <v>美妆</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -3022,48 +3135,48 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>category__home</v>
+        <v>shipping_included__yes</v>
       </c>
       <c r="B9" t="str">
-        <v>category</v>
+        <v>shipping_included</v>
       </c>
       <c r="C9" t="str">
-        <v>家居</v>
+        <v>是</v>
       </c>
       <c r="D9" t="str">
-        <v>家居</v>
+        <v>是</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>默认包邮。</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>category__beauty</v>
+        <v>shipping_included__no</v>
       </c>
       <c r="B10" t="str">
-        <v>category</v>
+        <v>shipping_included</v>
       </c>
       <c r="C10" t="str">
-        <v>美妆</v>
+        <v>否</v>
       </c>
       <c r="D10" t="str">
-        <v>美妆</v>
+        <v>否</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>非包邮。</v>
       </c>
     </row>
   </sheetData>
@@ -3099,16 +3212,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ad_type</v>
+        <v>shipping_included</v>
       </c>
       <c r="B2" t="str">
-        <v>广告类型</v>
+        <v>是否包邮</v>
       </c>
       <c r="C2" t="str">
-        <v>创建页和佣金表里使用的广告类型选项。</v>
+        <v>创建页当前包邮状态使用的选项。</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3119,16 +3232,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>category</v>
+        <v>ad_type</v>
       </c>
       <c r="B3" t="str">
-        <v>类目</v>
+        <v>广告类型</v>
       </c>
       <c r="C3" t="str">
-        <v>创建页和佣金表里使用的类目选项。</v>
+        <v>创建页和佣金表里使用的广告类型选项。</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3139,16 +3252,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>shipping_included</v>
+        <v>category</v>
       </c>
       <c r="B4" t="str">
-        <v>是否包邮</v>
+        <v>类目</v>
       </c>
       <c r="C4" t="str">
-        <v>创建页当前包邮状态使用的选项。</v>
+        <v>创建页和佣金表里使用的类目选项。</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>1</v>

--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -13,6 +13,7 @@
     <sheet name="app_options" sheetId="8" r:id="rId8"/>
     <sheet name="app_option_groups" sheetId="9" r:id="rId9"/>
     <sheet name="tpl_table_1776352156329_r4sw82" sheetId="10" r:id="rId10"/>
+    <sheet name="template_ui_config" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -509,6 +510,397 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F19"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>table_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>target_type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>target_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>prop_key</v>
+      </c>
+      <c r="E1" t="str">
+        <v>prop_value</v>
+      </c>
+      <c r="F1" t="str">
+        <v>sort</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B2" t="str">
+        <v>column</v>
+      </c>
+      <c r="C2" t="str">
+        <v>matchKey</v>
+      </c>
+      <c r="D2" t="str">
+        <v>label</v>
+      </c>
+      <c r="E2" t="str">
+        <v>类目</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B3" t="str">
+        <v>column</v>
+      </c>
+      <c r="C3" t="str">
+        <v>matchKey</v>
+      </c>
+      <c r="D3" t="str">
+        <v>placeholder</v>
+      </c>
+      <c r="E3" t="str">
+        <v>选择已配置类目</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B4" t="str">
+        <v>column</v>
+      </c>
+      <c r="C4" t="str">
+        <v>matchKey</v>
+      </c>
+      <c r="D4" t="str">
+        <v>control</v>
+      </c>
+      <c r="E4" t="str">
+        <v>select</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B5" t="str">
+        <v>column</v>
+      </c>
+      <c r="C5" t="str">
+        <v>matchKey</v>
+      </c>
+      <c r="D5" t="str">
+        <v>optionGroupKey</v>
+      </c>
+      <c r="E5" t="str">
+        <v>category</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B6" t="str">
+        <v>column</v>
+      </c>
+      <c r="C6" t="str">
+        <v>matchKey2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>label</v>
+      </c>
+      <c r="E6" t="str">
+        <v>广告类型</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B7" t="str">
+        <v>column</v>
+      </c>
+      <c r="C7" t="str">
+        <v>matchKey2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>placeholder</v>
+      </c>
+      <c r="E7" t="str">
+        <v>选择已配置广告类型</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B8" t="str">
+        <v>column</v>
+      </c>
+      <c r="C8" t="str">
+        <v>matchKey2</v>
+      </c>
+      <c r="D8" t="str">
+        <v>control</v>
+      </c>
+      <c r="E8" t="str">
+        <v>select</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B9" t="str">
+        <v>column</v>
+      </c>
+      <c r="C9" t="str">
+        <v>matchKey2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>optionGroupKey</v>
+      </c>
+      <c r="E9" t="str">
+        <v>ad_type</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B10" t="str">
+        <v>column</v>
+      </c>
+      <c r="C10" t="str">
+        <v>value</v>
+      </c>
+      <c r="D10" t="str">
+        <v>label</v>
+      </c>
+      <c r="E10" t="str">
+        <v>佣金费率</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B11" t="str">
+        <v>column</v>
+      </c>
+      <c r="C11" t="str">
+        <v>value</v>
+      </c>
+      <c r="D11" t="str">
+        <v>placeholder</v>
+      </c>
+      <c r="E11" t="str">
+        <v>例如 14</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B12" t="str">
+        <v>column</v>
+      </c>
+      <c r="C12" t="str">
+        <v>remark</v>
+      </c>
+      <c r="D12" t="str">
+        <v>label</v>
+      </c>
+      <c r="E12" t="str">
+        <v>备注</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B13" t="str">
+        <v>column</v>
+      </c>
+      <c r="C13" t="str">
+        <v>remark</v>
+      </c>
+      <c r="D13" t="str">
+        <v>placeholder</v>
+      </c>
+      <c r="E13" t="str">
+        <v>例如 官方后台查询结果</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B14" t="str">
+        <v>enum_pair_preset</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>fieldKey</v>
+      </c>
+      <c r="E14" t="str">
+        <v>matchKey2</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B15" t="str">
+        <v>enum_pair_preset</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>optionGroupKey</v>
+      </c>
+      <c r="E15" t="str">
+        <v>ad_type</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B16" t="str">
+        <v>column</v>
+      </c>
+      <c r="C16" t="str">
+        <v>matchKey</v>
+      </c>
+      <c r="D16" t="str">
+        <v>control</v>
+      </c>
+      <c r="E16" t="str">
+        <v>select</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B17" t="str">
+        <v>column</v>
+      </c>
+      <c r="C17" t="str">
+        <v>matchKey</v>
+      </c>
+      <c r="D17" t="str">
+        <v>optionGroupKey</v>
+      </c>
+      <c r="E17" t="str">
+        <v>category</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B18" t="str">
+        <v>column</v>
+      </c>
+      <c r="C18" t="str">
+        <v>matchKey2</v>
+      </c>
+      <c r="D18" t="str">
+        <v>control</v>
+      </c>
+      <c r="E18" t="str">
+        <v>select</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B19" t="str">
+        <v>column</v>
+      </c>
+      <c r="C19" t="str">
+        <v>matchKey2</v>
+      </c>
+      <c r="D19" t="str">
+        <v>optionGroupKey</v>
+      </c>
+      <c r="E19" t="str">
+        <v>ad_type</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J23"/>
@@ -1258,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1300,6 +1692,9 @@
       <c r="M1" t="str">
         <v>remark</v>
       </c>
+      <c r="N1" t="str">
+        <v>ui_config</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1341,6 +1736,9 @@
       <c r="M2" t="str">
         <v>来源页当前说明：79 以上不收固定费，12.50 以下按售价一半收取固定费。</v>
       </c>
+      <c r="N2" t="str">
+        <v>{"enumPairPresetSource":{},"columnOverrides":{}}</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1382,6 +1780,9 @@
       <c r="M3" t="str">
         <v>按重量和售价区间命中一行运费值。</v>
       </c>
+      <c r="N3" t="str">
+        <v>{"enumPairPresetSource":{},"columnOverrides":{}}</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1423,6 +1824,9 @@
       <c r="M4" t="str">
         <v>官方 79 以下可选快速免邮成本，按重量区间查值。</v>
       </c>
+      <c r="N4" t="str">
+        <v>{"enumPairPresetSource":{},"columnOverrides":{}}</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1464,6 +1868,9 @@
       <c r="M5" t="str">
         <v>来源页当前只明确给出费率范围：Clássico 为 10%~14%，Premium 为 15%~19%。类目细表未直接给出，这里先不写死猜测值。</v>
       </c>
+      <c r="N5" t="str">
+        <v>{"enumPairPresetSource":{"fieldKey":"matchKey2","optionGroupKey":"ad_type"},"columnOverrides":{"matchKey":{"label":"类目","placeholder":"选择已配置类目","control":"select","optionGroupKey":"category"},"matchKey2":{"label":"广告类型","placeholder":"选择已配置广告类型","control":"select","optionGroupKey":"ad_type"},"value":{"label":"佣金费率","placeholder":"例如 14"},"remark":{"label":"备注","placeholder":"例如 官方后台查询结果"}}}</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1505,10 +1912,13 @@
       <c r="M6" t="str">
         <v/>
       </c>
+      <c r="N6" t="str">
+        <v>{"enumPairPresetSource":{},"columnOverrides":{"matchKey":{"control":"select","optionGroupKey":"category"},"matchKey2":{"control":"select","optionGroupKey":"ad_type"}}}</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -14,6 +14,8 @@
     <sheet name="app_option_groups" sheetId="9" r:id="rId9"/>
     <sheet name="tpl_table_1776352156329_r4sw82" sheetId="10" r:id="rId10"/>
     <sheet name="template_ui_config" sheetId="11" r:id="rId11"/>
+    <sheet name="template_dimensions" sheetId="12" r:id="rId12"/>
+    <sheet name="template_result_columns" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -477,16 +479,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>match_key</v>
+        <v>参数 1</v>
       </c>
       <c r="B1" t="str">
-        <v>match_key_2</v>
+        <v>参数 2</v>
       </c>
       <c r="C1" t="str">
-        <v>value</v>
+        <v>结果值</v>
       </c>
       <c r="D1" t="str">
-        <v>remark</v>
+        <v>备注</v>
       </c>
     </row>
     <row r="2">
@@ -512,7 +514,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -776,42 +778,42 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ml_br_commission</v>
+        <v>table_1776352156329_r4sw82</v>
       </c>
       <c r="B14" t="str">
-        <v>enum_pair_preset</v>
+        <v>column</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>matchKey</v>
       </c>
       <c r="D14" t="str">
-        <v>fieldKey</v>
+        <v>control</v>
       </c>
       <c r="E14" t="str">
-        <v>matchKey2</v>
+        <v>select</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ml_br_commission</v>
+        <v>table_1776352156329_r4sw82</v>
       </c>
       <c r="B15" t="str">
-        <v>enum_pair_preset</v>
+        <v>column</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>matchKey</v>
       </c>
       <c r="D15" t="str">
         <v>optionGroupKey</v>
       </c>
       <c r="E15" t="str">
-        <v>ad_type</v>
+        <v>category</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -822,7 +824,7 @@
         <v>column</v>
       </c>
       <c r="C16" t="str">
-        <v>matchKey</v>
+        <v>matchKey2</v>
       </c>
       <c r="D16" t="str">
         <v>control</v>
@@ -831,7 +833,7 @@
         <v>select</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -842,61 +844,298 @@
         <v>column</v>
       </c>
       <c r="C17" t="str">
-        <v>matchKey</v>
+        <v>matchKey2</v>
       </c>
       <c r="D17" t="str">
         <v>optionGroupKey</v>
       </c>
       <c r="E17" t="str">
-        <v>category</v>
+        <v>ad_type</v>
       </c>
       <c r="F17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>table_1776352156329_r4sw82</v>
-      </c>
-      <c r="B18" t="str">
-        <v>column</v>
-      </c>
-      <c r="C18" t="str">
-        <v>matchKey2</v>
-      </c>
-      <c r="D18" t="str">
-        <v>control</v>
-      </c>
-      <c r="E18" t="str">
-        <v>select</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>table_1776352156329_r4sw82</v>
-      </c>
-      <c r="B19" t="str">
-        <v>column</v>
-      </c>
-      <c r="C19" t="str">
-        <v>matchKey2</v>
-      </c>
-      <c r="D19" t="str">
-        <v>optionGroupKey</v>
-      </c>
-      <c r="E19" t="str">
-        <v>ad_type</v>
-      </c>
-      <c r="F19">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>table_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>dimension_id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>field_name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="E1" t="str">
+        <v>sort</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ml_br_fixed_fee</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ml_br_fixed_fee__dimension__1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>参数 1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>range</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ml_br_shipping_fee</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ml_br_shipping_fee__dimension__1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>售价</v>
+      </c>
+      <c r="D3" t="str">
+        <v>range</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ml_br_shipping_fee</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ml_br_shipping_fee__dimension__2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>重量</v>
+      </c>
+      <c r="D4" t="str">
+        <v>range</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ml_br_shipping_fast_under_79</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ml_br_shipping_fast_under_79__dimension__1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>参数 1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>range</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ml_br_commission__dimension__1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>参数 1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>enum</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ml_br_commission__dimension__2</v>
+      </c>
+      <c r="C7" t="str">
+        <v>参数 2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>enum</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B8" t="str">
+        <v>table_1776352156329_r4sw82__dimension__1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>参数 1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>enum</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B9" t="str">
+        <v>table_1776352156329_r4sw82__dimension__2</v>
+      </c>
+      <c r="C9" t="str">
+        <v>参数 2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>enum</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>table_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>column_id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>label</v>
+      </c>
+      <c r="D1" t="str">
+        <v>type</v>
+      </c>
+      <c r="E1" t="str">
+        <v>sort</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ml_br_fixed_fee</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ml_br_fixed_fee__result__1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>结果值</v>
+      </c>
+      <c r="D2" t="str">
+        <v>number</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ml_br_shipping_fee</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ml_br_shipping_fee__result__1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>结果值</v>
+      </c>
+      <c r="D3" t="str">
+        <v>number</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ml_br_shipping_fast_under_79</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ml_br_shipping_fast_under_79__result__1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>结果值</v>
+      </c>
+      <c r="D4" t="str">
+        <v>number</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ml_br_commission</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ml_br_commission__result__1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>结果值</v>
+      </c>
+      <c r="D5" t="str">
+        <v>number</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>table_1776352156329_r4sw82</v>
+      </c>
+      <c r="B6" t="str">
+        <v>table_1776352156329_r4sw82__result__1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>结果值</v>
+      </c>
+      <c r="D6" t="str">
+        <v>number</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1869,7 +2108,7 @@
         <v>来源页当前只明确给出费率范围：Clássico 为 10%~14%，Premium 为 15%~19%。类目细表未直接给出，这里先不写死猜测值。</v>
       </c>
       <c r="N5" t="str">
-        <v>{"enumPairPresetSource":{"fieldKey":"matchKey2","optionGroupKey":"ad_type"},"columnOverrides":{"matchKey":{"label":"类目","placeholder":"选择已配置类目","control":"select","optionGroupKey":"category"},"matchKey2":{"label":"广告类型","placeholder":"选择已配置广告类型","control":"select","optionGroupKey":"ad_type"},"value":{"label":"佣金费率","placeholder":"例如 14"},"remark":{"label":"备注","placeholder":"例如 官方后台查询结果"}}}</v>
+        <v>{"columnOverrides":{"matchKey":{"label":"类目","placeholder":"选择已配置类目","control":"select","optionGroupKey":"category"},"matchKey2":{"label":"广告类型","placeholder":"选择已配置广告类型","control":"select","optionGroupKey":"ad_type"},"value":{"label":"佣金费率","placeholder":"例如 14"},"remark":{"label":"备注","placeholder":"例如 官方后台查询结果"}}}</v>
       </c>
     </row>
     <row r="6">
@@ -1913,7 +2152,7 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>{"enumPairPresetSource":{},"columnOverrides":{"matchKey":{"control":"select","optionGroupKey":"category"},"matchKey2":{"control":"select","optionGroupKey":"ad_type"}}}</v>
+        <v>{"columnOverrides":{"matchKey":{"control":"select","optionGroupKey":"category"},"matchKey2":{"control":"select","optionGroupKey":"ad_type"}}}</v>
       </c>
     </row>
   </sheetData>
@@ -1929,16 +2168,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>x_min</v>
+        <v>参数 1起始</v>
       </c>
       <c r="B1" t="str">
-        <v>x_max</v>
+        <v>参数 1结束</v>
       </c>
       <c r="C1" t="str">
-        <v>value</v>
+        <v>结果值</v>
       </c>
       <c r="D1" t="str">
-        <v>remark</v>
+        <v>备注</v>
       </c>
     </row>
     <row r="2">
@@ -1946,7 +2185,7 @@
         <v>12.5</v>
       </c>
       <c r="B2" t="str">
-        <v>29</v>
+        <v/>
       </c>
       <c r="C2" t="str">
         <v>6.25</v>
@@ -1960,7 +2199,7 @@
         <v>29</v>
       </c>
       <c r="B3" t="str">
-        <v>50</v>
+        <v/>
       </c>
       <c r="C3" t="str">
         <v>6.50</v>
@@ -1974,7 +2213,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="str">
-        <v>79</v>
+        <v/>
       </c>
       <c r="C4" t="str">
         <v>6.75</v>
@@ -1992,881 +2231,51 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>重量\售价</v>
+        <v>售价起始</v>
       </c>
       <c r="B1" t="str">
-        <v>19</v>
+        <v>售价结束</v>
       </c>
       <c r="C1" t="str">
-        <v>49</v>
+        <v>重量起始</v>
       </c>
       <c r="D1" t="str">
-        <v>79</v>
+        <v>重量结束</v>
       </c>
       <c r="E1" t="str">
-        <v>100</v>
+        <v>结果值</v>
       </c>
       <c r="F1" t="str">
-        <v>120</v>
-      </c>
-      <c r="G1" t="str">
-        <v>150</v>
-      </c>
-      <c r="H1" t="str">
-        <v>200</v>
-      </c>
-      <c r="I1" t="str">
-        <v>最后区间及以上</v>
+        <v>备注</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0.3</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>5.65</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>6.55</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>7.75</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>12.35</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>14.35</v>
-      </c>
-      <c r="G2" t="str">
-        <v>16.45</v>
-      </c>
-      <c r="H2" t="str">
-        <v>18.45</v>
-      </c>
-      <c r="I2" t="str">
-        <v>20.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="B3" t="str">
-        <v>5.95</v>
-      </c>
-      <c r="C3" t="str">
-        <v>6.65</v>
-      </c>
-      <c r="D3" t="str">
-        <v>7.85</v>
-      </c>
-      <c r="E3" t="str">
-        <v>13.25</v>
-      </c>
-      <c r="F3" t="str">
-        <v>15.45</v>
-      </c>
-      <c r="G3" t="str">
-        <v>17.65</v>
-      </c>
-      <c r="H3" t="str">
-        <v>19.85</v>
-      </c>
-      <c r="I3" t="str">
-        <v>22.55</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>1</v>
-      </c>
-      <c r="B4" t="str">
-        <v>6.05</v>
-      </c>
-      <c r="C4" t="str">
-        <v>6.75</v>
-      </c>
-      <c r="D4" t="str">
-        <v>7.95</v>
-      </c>
-      <c r="E4" t="str">
-        <v>13.85</v>
-      </c>
-      <c r="F4" t="str">
-        <v>16.15</v>
-      </c>
-      <c r="G4" t="str">
-        <v>18.45</v>
-      </c>
-      <c r="H4" t="str">
-        <v>20.75</v>
-      </c>
-      <c r="I4" t="str">
-        <v>23.65</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>1.5</v>
-      </c>
-      <c r="B5" t="str">
-        <v>6.15</v>
-      </c>
-      <c r="C5" t="str">
-        <v>6.85</v>
-      </c>
-      <c r="D5" t="str">
-        <v>8.05</v>
-      </c>
-      <c r="E5" t="str">
-        <v>14.15</v>
-      </c>
-      <c r="F5" t="str">
-        <v>16.45</v>
-      </c>
-      <c r="G5" t="str">
-        <v>18.85</v>
-      </c>
-      <c r="H5" t="str">
-        <v>21.15</v>
-      </c>
-      <c r="I5" t="str">
-        <v>24.65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>6.25</v>
-      </c>
-      <c r="C6" t="str">
-        <v>6.95</v>
-      </c>
-      <c r="D6" t="str">
-        <v>8.15</v>
-      </c>
-      <c r="E6" t="str">
-        <v>14.45</v>
-      </c>
-      <c r="F6" t="str">
-        <v>16.85</v>
-      </c>
-      <c r="G6" t="str">
-        <v>19.25</v>
-      </c>
-      <c r="H6" t="str">
-        <v>21.65</v>
-      </c>
-      <c r="I6" t="str">
-        <v>24.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>6.35</v>
-      </c>
-      <c r="C7" t="str">
-        <v>7.95</v>
-      </c>
-      <c r="D7" t="str">
-        <v>8.55</v>
-      </c>
-      <c r="E7" t="str">
-        <v>15.75</v>
-      </c>
-      <c r="F7" t="str">
-        <v>18.35</v>
-      </c>
-      <c r="G7" t="str">
-        <v>21.05</v>
-      </c>
-      <c r="H7" t="str">
-        <v>23.65</v>
-      </c>
-      <c r="I7" t="str">
-        <v>26.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>4</v>
-      </c>
-      <c r="B8" t="str">
-        <v>6.45</v>
-      </c>
-      <c r="C8" t="str">
-        <v>8.15</v>
-      </c>
-      <c r="D8" t="str">
-        <v>8.95</v>
-      </c>
-      <c r="E8" t="str">
-        <v>17.05</v>
-      </c>
-      <c r="F8" t="str">
-        <v>19.85</v>
-      </c>
-      <c r="G8" t="str">
-        <v>22.65</v>
-      </c>
-      <c r="H8" t="str">
-        <v>25.55</v>
-      </c>
-      <c r="I8" t="str">
-        <v>28.35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>6.55</v>
-      </c>
-      <c r="C9" t="str">
-        <v>8.35</v>
-      </c>
-      <c r="D9" t="str">
-        <v>9.75</v>
-      </c>
-      <c r="E9" t="str">
-        <v>18.45</v>
-      </c>
-      <c r="F9" t="str">
-        <v>21.55</v>
-      </c>
-      <c r="G9" t="str">
-        <v>24.65</v>
-      </c>
-      <c r="H9" t="str">
-        <v>27.75</v>
-      </c>
-      <c r="I9" t="str">
-        <v>30.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6</v>
-      </c>
-      <c r="B10" t="str">
-        <v>6.65</v>
-      </c>
-      <c r="C10" t="str">
-        <v>8.55</v>
-      </c>
-      <c r="D10" t="str">
-        <v>9.95</v>
-      </c>
-      <c r="E10" t="str">
-        <v>25.45</v>
-      </c>
-      <c r="F10" t="str">
-        <v>28.55</v>
-      </c>
-      <c r="G10" t="str">
-        <v>32.65</v>
-      </c>
-      <c r="H10" t="str">
-        <v>35.75</v>
-      </c>
-      <c r="I10" t="str">
-        <v>39.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>7</v>
-      </c>
-      <c r="B11" t="str">
-        <v>6.75</v>
-      </c>
-      <c r="C11" t="str">
-        <v>8.75</v>
-      </c>
-      <c r="D11" t="str">
-        <v>10.15</v>
-      </c>
-      <c r="E11" t="str">
-        <v>27.05</v>
-      </c>
-      <c r="F11" t="str">
-        <v>31.05</v>
-      </c>
-      <c r="G11" t="str">
-        <v>36.05</v>
-      </c>
-      <c r="H11" t="str">
-        <v>40.05</v>
-      </c>
-      <c r="I11" t="str">
-        <v>44.05</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>8</v>
-      </c>
-      <c r="B12" t="str">
-        <v>6.85</v>
-      </c>
-      <c r="C12" t="str">
-        <v>8.95</v>
-      </c>
-      <c r="D12" t="str">
-        <v>10.35</v>
-      </c>
-      <c r="E12" t="str">
-        <v>28.85</v>
-      </c>
-      <c r="F12" t="str">
-        <v>33.65</v>
-      </c>
-      <c r="G12" t="str">
-        <v>38.45</v>
-      </c>
-      <c r="H12" t="str">
-        <v>43.25</v>
-      </c>
-      <c r="I12" t="str">
-        <v>48.05</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>9</v>
-      </c>
-      <c r="B13" t="str">
-        <v>6.95</v>
-      </c>
-      <c r="C13" t="str">
-        <v>9.15</v>
-      </c>
-      <c r="D13" t="str">
-        <v>10.55</v>
-      </c>
-      <c r="E13" t="str">
-        <v>29.65</v>
-      </c>
-      <c r="F13" t="str">
-        <v>34.55</v>
-      </c>
-      <c r="G13" t="str">
-        <v>39.55</v>
-      </c>
-      <c r="H13" t="str">
-        <v>44.45</v>
-      </c>
-      <c r="I13" t="str">
-        <v>49.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>11</v>
-      </c>
-      <c r="B14" t="str">
-        <v>7.05</v>
-      </c>
-      <c r="C14" t="str">
-        <v>9.55</v>
-      </c>
-      <c r="D14" t="str">
-        <v>10.95</v>
-      </c>
-      <c r="E14" t="str">
-        <v>41.25</v>
-      </c>
-      <c r="F14" t="str">
-        <v>48.05</v>
-      </c>
-      <c r="G14" t="str">
-        <v>54.95</v>
-      </c>
-      <c r="H14" t="str">
-        <v>61.75</v>
-      </c>
-      <c r="I14" t="str">
-        <v>68.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>13</v>
-      </c>
-      <c r="B15" t="str">
-        <v>7.15</v>
-      </c>
-      <c r="C15" t="str">
-        <v>9.95</v>
-      </c>
-      <c r="D15" t="str">
-        <v>11.35</v>
-      </c>
-      <c r="E15" t="str">
-        <v>42.15</v>
-      </c>
-      <c r="F15" t="str">
-        <v>49.25</v>
-      </c>
-      <c r="G15" t="str">
-        <v>56.25</v>
-      </c>
-      <c r="H15" t="str">
-        <v>63.25</v>
-      </c>
-      <c r="I15" t="str">
-        <v>70.25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>7.25</v>
-      </c>
-      <c r="C16" t="str">
-        <v>10.15</v>
-      </c>
-      <c r="D16" t="str">
-        <v>11.55</v>
-      </c>
-      <c r="E16" t="str">
-        <v>45.05</v>
-      </c>
-      <c r="F16" t="str">
-        <v>52.45</v>
-      </c>
-      <c r="G16" t="str">
-        <v>59.95</v>
-      </c>
-      <c r="H16" t="str">
-        <v>67.45</v>
-      </c>
-      <c r="I16" t="str">
-        <v>74.95</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>17</v>
-      </c>
-      <c r="B17" t="str">
-        <v>7.35</v>
-      </c>
-      <c r="C17" t="str">
-        <v>10.35</v>
-      </c>
-      <c r="D17" t="str">
-        <v>11.75</v>
-      </c>
-      <c r="E17" t="str">
-        <v>48.55</v>
-      </c>
-      <c r="F17" t="str">
-        <v>56.05</v>
-      </c>
-      <c r="G17" t="str">
-        <v>63.55</v>
-      </c>
-      <c r="H17" t="str">
-        <v>70.75</v>
-      </c>
-      <c r="I17" t="str">
-        <v>78.65</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>20</v>
-      </c>
-      <c r="B18" t="str">
-        <v>7.45</v>
-      </c>
-      <c r="C18" t="str">
-        <v>10.55</v>
-      </c>
-      <c r="D18" t="str">
-        <v>11.95</v>
-      </c>
-      <c r="E18" t="str">
-        <v>54.75</v>
-      </c>
-      <c r="F18" t="str">
-        <v>63.85</v>
-      </c>
-      <c r="G18" t="str">
-        <v>72.95</v>
-      </c>
-      <c r="H18" t="str">
-        <v>82.05</v>
-      </c>
-      <c r="I18" t="str">
-        <v>91.15</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>25</v>
-      </c>
-      <c r="B19" t="str">
-        <v>7.65</v>
-      </c>
-      <c r="C19" t="str">
-        <v>10.95</v>
-      </c>
-      <c r="D19" t="str">
-        <v>12.15</v>
-      </c>
-      <c r="E19" t="str">
-        <v>64.05</v>
-      </c>
-      <c r="F19" t="str">
-        <v>75.05</v>
-      </c>
-      <c r="G19" t="str">
-        <v>84.75</v>
-      </c>
-      <c r="H19" t="str">
-        <v>95.35</v>
-      </c>
-      <c r="I19" t="str">
-        <v>105.95</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>30</v>
-      </c>
-      <c r="B20" t="str">
-        <v>7.75</v>
-      </c>
-      <c r="C20" t="str">
-        <v>11.15</v>
-      </c>
-      <c r="D20" t="str">
-        <v>12.35</v>
-      </c>
-      <c r="E20" t="str">
-        <v>65.95</v>
-      </c>
-      <c r="F20" t="str">
-        <v>75.45</v>
-      </c>
-      <c r="G20" t="str">
-        <v>85.55</v>
-      </c>
-      <c r="H20" t="str">
-        <v>96.25</v>
-      </c>
-      <c r="I20" t="str">
-        <v>106.95</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>40</v>
-      </c>
-      <c r="B21" t="str">
-        <v>7.85</v>
-      </c>
-      <c r="C21" t="str">
-        <v>11.35</v>
-      </c>
-      <c r="D21" t="str">
-        <v>12.55</v>
-      </c>
-      <c r="E21" t="str">
-        <v>67.75</v>
-      </c>
-      <c r="F21" t="str">
-        <v>78.95</v>
-      </c>
-      <c r="G21" t="str">
-        <v>88.95</v>
-      </c>
-      <c r="H21" t="str">
-        <v>99.15</v>
-      </c>
-      <c r="I21" t="str">
-        <v>107.05</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>50</v>
-      </c>
-      <c r="B22" t="str">
-        <v>7.95</v>
-      </c>
-      <c r="C22" t="str">
-        <v>11.55</v>
-      </c>
-      <c r="D22" t="str">
-        <v>12.75</v>
-      </c>
-      <c r="E22" t="str">
-        <v>70.25</v>
-      </c>
-      <c r="F22" t="str">
-        <v>81.05</v>
-      </c>
-      <c r="G22" t="str">
-        <v>92.05</v>
-      </c>
-      <c r="H22" t="str">
-        <v>102.55</v>
-      </c>
-      <c r="I22" t="str">
-        <v>110.75</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>60</v>
-      </c>
-      <c r="B23" t="str">
-        <v>8.05</v>
-      </c>
-      <c r="C23" t="str">
-        <v>11.75</v>
-      </c>
-      <c r="D23" t="str">
-        <v>12.95</v>
-      </c>
-      <c r="E23" t="str">
-        <v>74.95</v>
-      </c>
-      <c r="F23" t="str">
-        <v>86.45</v>
-      </c>
-      <c r="G23" t="str">
-        <v>98.15</v>
-      </c>
-      <c r="H23" t="str">
-        <v>109.35</v>
-      </c>
-      <c r="I23" t="str">
-        <v>118.15</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>70</v>
-      </c>
-      <c r="B24" t="str">
-        <v>8.15</v>
-      </c>
-      <c r="C24" t="str">
-        <v>11.95</v>
-      </c>
-      <c r="D24" t="str">
-        <v>13.15</v>
-      </c>
-      <c r="E24" t="str">
-        <v>80.25</v>
-      </c>
-      <c r="F24" t="str">
-        <v>92.95</v>
-      </c>
-      <c r="G24" t="str">
-        <v>105.05</v>
-      </c>
-      <c r="H24" t="str">
-        <v>117.15</v>
-      </c>
-      <c r="I24" t="str">
-        <v>126.55</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>80</v>
-      </c>
-      <c r="B25" t="str">
-        <v>8.25</v>
-      </c>
-      <c r="C25" t="str">
-        <v>12.15</v>
-      </c>
-      <c r="D25" t="str">
-        <v>13.35</v>
-      </c>
-      <c r="E25" t="str">
-        <v>83.95</v>
-      </c>
-      <c r="F25" t="str">
-        <v>97.05</v>
-      </c>
-      <c r="G25" t="str">
-        <v>109.85</v>
-      </c>
-      <c r="H25" t="str">
-        <v>122.45</v>
-      </c>
-      <c r="I25" t="str">
-        <v>132.25</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>90</v>
-      </c>
-      <c r="B26" t="str">
-        <v>8.35</v>
-      </c>
-      <c r="C26" t="str">
-        <v>12.35</v>
-      </c>
-      <c r="D26" t="str">
-        <v>13.55</v>
-      </c>
-      <c r="E26" t="str">
-        <v>93.25</v>
-      </c>
-      <c r="F26" t="str">
-        <v>107.45</v>
-      </c>
-      <c r="G26" t="str">
-        <v>122.05</v>
-      </c>
-      <c r="H26" t="str">
-        <v>136.05</v>
-      </c>
-      <c r="I26" t="str">
-        <v>146.95</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>100</v>
-      </c>
-      <c r="B27" t="str">
-        <v>8.45</v>
-      </c>
-      <c r="C27" t="str">
-        <v>12.55</v>
-      </c>
-      <c r="D27" t="str">
-        <v>13.75</v>
-      </c>
-      <c r="E27" t="str">
-        <v>106.55</v>
-      </c>
-      <c r="F27" t="str">
-        <v>123.95</v>
-      </c>
-      <c r="G27" t="str">
-        <v>139.55</v>
-      </c>
-      <c r="H27" t="str">
-        <v>155.55</v>
-      </c>
-      <c r="I27" t="str">
-        <v>167.95</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>125</v>
-      </c>
-      <c r="B28" t="str">
-        <v>8.55</v>
-      </c>
-      <c r="C28" t="str">
-        <v>12.75</v>
-      </c>
-      <c r="D28" t="str">
-        <v>13.95</v>
-      </c>
-      <c r="E28" t="str">
-        <v>119.25</v>
-      </c>
-      <c r="F28" t="str">
-        <v>138.05</v>
-      </c>
-      <c r="G28" t="str">
-        <v>156.05</v>
-      </c>
-      <c r="H28" t="str">
-        <v>173.95</v>
-      </c>
-      <c r="I28" t="str">
-        <v>187.95</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>150</v>
-      </c>
-      <c r="B29" t="str">
-        <v>8.65</v>
-      </c>
-      <c r="C29" t="str">
-        <v>12.75</v>
-      </c>
-      <c r="D29" t="str">
-        <v>14.15</v>
-      </c>
-      <c r="E29" t="str">
-        <v>126.55</v>
-      </c>
-      <c r="F29" t="str">
-        <v>146.15</v>
-      </c>
-      <c r="G29" t="str">
-        <v>165.65</v>
-      </c>
-      <c r="H29" t="str">
-        <v>184.65</v>
-      </c>
-      <c r="I29" t="str">
-        <v>199.45</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>150+</v>
-      </c>
-      <c r="B30" t="str">
-        <v>8.75</v>
-      </c>
-      <c r="C30" t="str">
-        <v>12.95</v>
-      </c>
-      <c r="D30" t="str">
-        <v>14.35</v>
-      </c>
-      <c r="E30" t="str">
-        <v>166.15</v>
-      </c>
-      <c r="F30" t="str">
-        <v>192.45</v>
-      </c>
-      <c r="G30" t="str">
-        <v>217.55</v>
-      </c>
-      <c r="H30" t="str">
-        <v>242.55</v>
-      </c>
-      <c r="I30" t="str">
-        <v>261.95</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2877,16 +2286,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>x_min</v>
+        <v>参数 1起始</v>
       </c>
       <c r="B1" t="str">
-        <v>x_max</v>
+        <v>参数 1结束</v>
       </c>
       <c r="C1" t="str">
-        <v>value</v>
+        <v>结果值</v>
       </c>
       <c r="D1" t="str">
-        <v>remark</v>
+        <v>备注</v>
       </c>
     </row>
     <row r="2">
@@ -3308,16 +2717,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>match_key</v>
+        <v>参数 1</v>
       </c>
       <c r="B1" t="str">
-        <v>match_key_2</v>
+        <v>参数 2</v>
       </c>
       <c r="C1" t="str">
-        <v>value</v>
+        <v>结果值</v>
       </c>
       <c r="D1" t="str">
-        <v>remark</v>
+        <v>备注</v>
       </c>
     </row>
     <row r="2">
